--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{501F66FE-AC02-41D5-A477-9B59137BF8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBE5328-C005-46DD-AA4E-2F0F59533005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <sheet name="Sales_Stage_Details" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="361">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1123,23 +1122,21 @@
     <t>Humain, Riyadh Air, Expo, Nestle, Kpmg, EY, Accenture, NCFB</t>
   </si>
   <si>
-    <t xml:space="preserve">MEP , Nadec </t>
-  </si>
-  <si>
     <t>MEP, ITQAN, Humain, Expo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadec </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="[$SAR]\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1259,7 +1256,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1298,28 +1295,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1393,32 +1374,26 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
@@ -1732,21 +1707,21 @@
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1779,12 +1754,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -3903,7 +3878,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3961,7 +3936,7 @@
       <c r="D5" t="s">
         <v>350</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="37">
         <v>330000</v>
       </c>
       <c r="G5" t="s">
@@ -3975,69 +3950,83 @@
       <c r="B6" t="s">
         <v>349</v>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="E6" s="38">
-        <v>1000000</v>
+      <c r="C6" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" s="37">
+        <v>500000</v>
       </c>
       <c r="G6" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>342</v>
       </c>
       <c r="B7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>358</v>
-      </c>
-      <c r="E7" s="36">
-        <v>2700000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="E7" s="37">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B8" t="s">
         <v>353</v>
       </c>
-      <c r="C8" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="E8">
-        <v>2100000</v>
+      <c r="C8" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="E8" s="37">
+        <v>2700000</v>
       </c>
       <c r="G8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>343</v>
       </c>
       <c r="B9" t="s">
         <v>353</v>
       </c>
+      <c r="C9" s="32" t="s">
+        <v>359</v>
+      </c>
+      <c r="E9" s="37">
+        <v>2100000</v>
+      </c>
       <c r="G9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B10" t="s">
         <v>353</v>
       </c>
       <c r="G10" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G11" t="s">
         <v>357</v>
       </c>
     </row>
@@ -4063,11 +4052,11 @@
       <c r="A1" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5490,29 +5479,29 @@
       <c r="A1" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -5589,14 +5578,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -6761,29 +6750,29 @@
       <c r="A1" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -6860,14 +6849,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -8114,29 +8103,29 @@
       <c r="A1" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -8155,10 +8144,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="34"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -8224,11 +8213,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -8264,10 +8253,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="34"/>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8319,10 +8308,10 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="32"/>
+      <c r="B25" s="34"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9367,32 +9356,32 @@
       <c r="A1" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -9440,13 +9429,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -9798,14 +9787,14 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="36" t="s">
         <v>244</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -10906,25 +10895,25 @@
       <c r="A1" s="33" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -12547,21 +12536,21 @@
       <c r="A1" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -13697,36 +13686,36 @@
       <c r="A1" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -13881,13 +13870,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
       <c r="G9" s="26">
         <v>0.6</v>
       </c>
@@ -14043,17 +14032,17 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="36" t="s">
         <v>335</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="B16" s="32"/>
+      <c r="B16" s="34"/>
       <c r="G16" s="18" t="s">
         <v>337</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBE5328-C005-46DD-AA4E-2F0F59533005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D818FF24-87B0-46C3-9FBB-A7547DDECB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="368">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1119,13 +1119,34 @@
     <t>Add weekly won detail here if needed.</t>
   </si>
   <si>
-    <t>Humain, Riyadh Air, Expo, Nestle, Kpmg, EY, Accenture, NCFB</t>
-  </si>
-  <si>
-    <t>MEP, ITQAN, Humain, Expo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nadec </t>
+  </si>
+  <si>
+    <t>Riyadh Air</t>
+  </si>
+  <si>
+    <t>Expo</t>
+  </si>
+  <si>
+    <t>Nestle</t>
+  </si>
+  <si>
+    <t>Kpmg</t>
+  </si>
+  <si>
+    <t>EY</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>NCFB</t>
+  </si>
+  <si>
+    <t>Humain</t>
+  </si>
+  <si>
+    <t>CFG</t>
   </si>
 </sst>
 </file>
@@ -1138,11 +1159,18 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1224,6 +1252,14 @@
       <sz val="14"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1298,99 +1334,109 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1704,7 +1750,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="34"/>
@@ -1714,7 +1760,7 @@
       <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="34"/>
@@ -3878,7 +3924,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3936,7 +3982,7 @@
       <c r="D5" t="s">
         <v>350</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="32">
         <v>330000</v>
       </c>
       <c r="G5" t="s">
@@ -3944,16 +3990,16 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="37" t="s">
         <v>342</v>
       </c>
       <c r="B6" t="s">
         <v>349</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="32">
         <v>500000</v>
       </c>
       <c r="G6" t="s">
@@ -3961,72 +4007,250 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="37" t="s">
         <v>342</v>
       </c>
       <c r="B7" t="s">
         <v>349</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="E7" s="37">
+      <c r="C7" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="32">
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>342</v>
-      </c>
-      <c r="B8" t="s">
-        <v>353</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="E8" s="37">
-        <v>2700000</v>
-      </c>
-      <c r="G8" t="s">
-        <v>354</v>
-      </c>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="37"/>
+      <c r="C8" s="31"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B9" t="s">
         <v>353</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="E9" s="37">
-        <v>2100000</v>
+      <c r="C9" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="E9" s="32">
+        <v>500000</v>
       </c>
       <c r="G9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>250</v>
+        <v>342</v>
       </c>
       <c r="B10" t="s">
         <v>353</v>
       </c>
-      <c r="G10" t="s">
-        <v>356</v>
+      <c r="C10" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="E10" s="32">
+        <v>500000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="B11" t="s">
         <v>353</v>
       </c>
-      <c r="G11" t="s">
+      <c r="C11" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="E11" s="32">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="E12" s="32">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B13" t="s">
+        <v>353</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="E13" s="32">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="E14" s="32">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B15" t="s">
+        <v>353</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="E15" s="32">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="E16" s="32">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C17" s="38"/>
+      <c r="E17" s="32"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>343</v>
+      </c>
+      <c r="B18" t="s">
+        <v>353</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="32">
+        <v>500000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B19" t="s">
+        <v>353</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="E19" s="32">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>343</v>
+      </c>
+      <c r="B20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="E20" s="32">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>343</v>
+      </c>
+      <c r="B21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="E21" s="32">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C22" s="39"/>
+      <c r="E22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23" t="s">
+        <v>353</v>
+      </c>
+      <c r="C23" t="s">
+        <v>367</v>
+      </c>
+      <c r="G23" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25" t="s">
+        <v>349</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B26" t="s">
+        <v>353</v>
+      </c>
+      <c r="G26" t="s">
         <v>357</v>
       </c>
     </row>
@@ -4049,7 +4273,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="34"/>
@@ -5476,7 +5700,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="34"/>
@@ -5486,7 +5710,7 @@
       <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>112</v>
       </c>
       <c r="B2" s="34"/>
@@ -6747,7 +6971,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="34"/>
@@ -6757,7 +6981,7 @@
       <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>139</v>
       </c>
       <c r="B2" s="34"/>
@@ -8100,7 +8324,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="34"/>
@@ -8111,7 +8335,7 @@
       <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>154</v>
       </c>
       <c r="B2" s="34"/>
@@ -9353,7 +9577,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="34"/>
@@ -9365,7 +9589,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>204</v>
       </c>
       <c r="B2" s="34"/>
@@ -10892,7 +11116,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>246</v>
       </c>
       <c r="B1" s="34"/>
@@ -10904,7 +11128,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>247</v>
       </c>
       <c r="B2" s="34"/>
@@ -12533,7 +12757,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>297</v>
       </c>
       <c r="B1" s="34"/>
@@ -12543,7 +12767,7 @@
       <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>298</v>
       </c>
       <c r="B2" s="34"/>
@@ -13683,7 +13907,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>87</v>
       </c>
       <c r="B1" s="34"/>
@@ -13695,7 +13919,7 @@
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>315</v>
       </c>
       <c r="B2" s="34"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D818FF24-87B0-46C3-9FBB-A7547DDECB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1283B627-3D81-4776-A13B-806092F5E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="366">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1093,12 +1093,6 @@
   </si>
   <si>
     <t>This Month</t>
-  </si>
-  <si>
-    <t>Active pipeline item</t>
-  </si>
-  <si>
-    <t>Auto-seeded from Pipeline_Revenue</t>
   </si>
   <si>
     <t>Add lead rows here if you want the dashboard to show client-level detail for leads.</t>
@@ -1178,17 +1172,20 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1196,12 +1193,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1209,6 +1208,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1216,29 +1216,34 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1246,11 +1251,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1336,7 +1343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1414,6 +1421,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1423,19 +1440,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1750,24 +1754,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1800,12 +1804,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -3924,7 +3928,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3970,76 +3974,79 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>343</v>
+      <c r="A5" s="33" t="s">
+        <v>342</v>
       </c>
       <c r="B5" t="s">
         <v>349</v>
       </c>
-      <c r="C5" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="32">
+        <v>500000</v>
+      </c>
+      <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="E5" s="32">
-        <v>330000</v>
-      </c>
-      <c r="G5" t="s">
-        <v>351</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="33" t="s">
         <v>342</v>
       </c>
       <c r="B6" t="s">
         <v>349</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>224</v>
+        <v>356</v>
       </c>
       <c r="E6" s="32">
         <v>500000</v>
       </c>
-      <c r="G6" t="s">
-        <v>352</v>
-      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" t="s">
         <v>342</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>358</v>
+        <v>351</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>364</v>
       </c>
       <c r="E7" s="32">
         <v>500000</v>
       </c>
+      <c r="G7" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="C8" s="31"/>
-      <c r="E8" s="32"/>
+      <c r="A8" t="s">
+        <v>342</v>
+      </c>
+      <c r="B8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="E8" s="32">
+        <v>500000</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>342</v>
       </c>
       <c r="B9" t="s">
-        <v>353</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>366</v>
+        <v>351</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>358</v>
       </c>
       <c r="E9" s="32">
-        <v>500000</v>
-      </c>
-      <c r="G9" t="s">
-        <v>354</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -4047,13 +4054,13 @@
         <v>342</v>
       </c>
       <c r="B10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C10" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>359</v>
       </c>
       <c r="E10" s="32">
-        <v>500000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -4061,13 +4068,13 @@
         <v>342</v>
       </c>
       <c r="B11" t="s">
-        <v>353</v>
-      </c>
-      <c r="C11" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>360</v>
       </c>
       <c r="E11" s="32">
-        <v>700000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4075,13 +4082,13 @@
         <v>342</v>
       </c>
       <c r="B12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C12" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>361</v>
       </c>
       <c r="E12" s="32">
-        <v>200000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -4089,9 +4096,9 @@
         <v>342</v>
       </c>
       <c r="B13" t="s">
-        <v>353</v>
-      </c>
-      <c r="C13" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>362</v>
       </c>
       <c r="E13" s="32">
@@ -4103,155 +4110,128 @@
         <v>342</v>
       </c>
       <c r="B14" t="s">
-        <v>353</v>
-      </c>
-      <c r="C14" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C14" s="34" t="s">
         <v>363</v>
       </c>
       <c r="E14" s="32">
-        <v>100000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="32">
+        <v>500000</v>
+      </c>
+      <c r="G15" t="s">
         <v>353</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="E15" s="32">
-        <v>100000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B16" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="E16" s="32">
+        <v>400000</v>
+      </c>
+      <c r="G16" t="s">
         <v>353</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>365</v>
-      </c>
-      <c r="E16" s="32">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>343</v>
+      </c>
+      <c r="B17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>364</v>
+      </c>
+      <c r="E17" s="32">
         <v>500000</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C17" s="38"/>
-      <c r="E17" s="32"/>
+      <c r="G17" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>343</v>
       </c>
       <c r="B18" t="s">
+        <v>351</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="E18" s="32">
+        <v>700000</v>
+      </c>
+      <c r="G18" t="s">
         <v>353</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="E18" s="32">
-        <v>500000</v>
-      </c>
-      <c r="G18" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>343</v>
+        <v>250</v>
       </c>
       <c r="B19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="E19" s="32">
-        <v>400000</v>
+        <v>351</v>
+      </c>
+      <c r="C19" t="s">
+        <v>365</v>
+      </c>
+      <c r="G19" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>343</v>
+        <v>250</v>
       </c>
       <c r="B20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="E20" s="32">
-        <v>500000</v>
+        <v>351</v>
+      </c>
+      <c r="C20" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>343</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s">
-        <v>353</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>360</v>
-      </c>
-      <c r="E21" s="32">
-        <v>700000</v>
+        <v>349</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C22" s="39"/>
-      <c r="E22" s="32"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>250</v>
-      </c>
-      <c r="B23" t="s">
-        <v>353</v>
-      </c>
-      <c r="C23" t="s">
-        <v>367</v>
-      </c>
-      <c r="G23" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>250</v>
-      </c>
-      <c r="B24" t="s">
-        <v>353</v>
-      </c>
-      <c r="C24" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>250</v>
-      </c>
-      <c r="B25" t="s">
-        <v>349</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A22" t="s">
         <v>269</v>
       </c>
-      <c r="B26" t="s">
-        <v>353</v>
-      </c>
-      <c r="G26" t="s">
-        <v>357</v>
+      <c r="B22" t="s">
+        <v>351</v>
+      </c>
+      <c r="G22" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4273,14 +4253,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5700,32 +5680,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -5802,14 +5782,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -6971,32 +6951,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -7073,14 +7053,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -8324,32 +8304,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="38"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -8368,10 +8348,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="38"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -8437,11 +8417,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -8477,10 +8457,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="34"/>
+      <c r="B17" s="38"/>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8532,10 +8512,10 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="34"/>
+      <c r="B25" s="38"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9577,35 +9557,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -9653,13 +9633,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -10011,14 +9991,14 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -11116,28 +11096,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -12757,24 +12737,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -13907,39 +13887,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -14094,13 +14074,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
       <c r="G9" s="26">
         <v>0.6</v>
       </c>
@@ -14256,17 +14236,17 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="B16" s="34"/>
+      <c r="B16" s="38"/>
       <c r="G16" s="18" t="s">
         <v>337</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1283B627-3D81-4776-A13B-806092F5E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26C8F60-6860-4298-9314-111E2DBDCE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -13993,8 +13993,7 @@
         <v>2095000</v>
       </c>
       <c r="D6" s="13">
-        <f>COUNTIF(Pipeline_Revenue!A11:A19,"Apr")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="13">
@@ -14024,8 +14023,7 @@
         <v>3275000</v>
       </c>
       <c r="D7" s="13">
-        <f>COUNTIFS(Sales_Raw_Opportunities!H:H,"Submitted",Sales_Raw_Opportunities!D:D,"Apr 2026")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="13">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26C8F60-6860-4298-9314-111E2DBDCE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48A841A-E8CE-4946-9244-05369DA02425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="366">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1435,10 +1435,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1754,7 +1754,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="38"/>
@@ -1804,7 +1804,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="39" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="38"/>
@@ -3928,7 +3928,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4219,18 +4219,29 @@
       <c r="B21" t="s">
         <v>349</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>221</v>
+      <c r="G21" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B22" t="s">
+        <v>349</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>269</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>351</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G23" t="s">
         <v>355</v>
       </c>
     </row>
@@ -4253,7 +4264,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="38"/>
@@ -5680,7 +5691,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="38"/>
@@ -5700,7 +5711,7 @@
       <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="38"/>
@@ -5782,7 +5793,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="39" t="s">
         <v>126</v>
       </c>
       <c r="B9" s="38"/>
@@ -6951,7 +6962,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="38"/>
@@ -6971,7 +6982,7 @@
       <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="38"/>
@@ -7053,7 +7064,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="39" t="s">
         <v>148</v>
       </c>
       <c r="B9" s="38"/>
@@ -8304,7 +8315,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="38"/>
@@ -8326,7 +8337,7 @@
       <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="38"/>
@@ -8348,7 +8359,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="39" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="38"/>
@@ -8417,7 +8428,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="39" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="38"/>
@@ -8457,7 +8468,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="39" t="s">
         <v>181</v>
       </c>
       <c r="B17" s="38"/>
@@ -8512,7 +8523,7 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="39" t="s">
         <v>194</v>
       </c>
       <c r="B25" s="38"/>
@@ -9557,7 +9568,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="38"/>
@@ -9581,7 +9592,7 @@
       <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="38"/>
@@ -9633,7 +9644,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="39" t="s">
         <v>212</v>
       </c>
       <c r="B9" s="38"/>
@@ -9991,7 +10002,7 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="39" t="s">
         <v>244</v>
       </c>
       <c r="B25" s="38"/>
@@ -11096,7 +11107,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>246</v>
       </c>
       <c r="B1" s="38"/>
@@ -12737,7 +12748,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>297</v>
       </c>
       <c r="B1" s="38"/>
@@ -13887,7 +13898,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>87</v>
       </c>
       <c r="B1" s="38"/>
@@ -13911,7 +13922,7 @@
       <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>316</v>
       </c>
       <c r="B3" s="38"/>
@@ -14072,7 +14083,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="39" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="38"/>
@@ -14234,14 +14245,14 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="39" t="s">
         <v>335</v>
       </c>
       <c r="B15" s="38"/>
       <c r="C15" s="38"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="39" t="s">
         <v>336</v>
       </c>
       <c r="B16" s="38"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48A841A-E8CE-4946-9244-05369DA02425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5199EE23-8AA3-4944-8666-C21C9A0FC70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="367">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1141,6 +1141,9 @@
   </si>
   <si>
     <t>CFG</t>
+  </si>
+  <si>
+    <t>SAR 100,000</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1338,12 +1341,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1435,11 +1453,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1754,7 +1775,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="38"/>
@@ -1804,7 +1825,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="40" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="38"/>
@@ -4219,6 +4240,12 @@
       <c r="B21" t="s">
         <v>349</v>
       </c>
+      <c r="C21" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>366</v>
+      </c>
       <c r="G21" t="s">
         <v>354</v>
       </c>
@@ -4264,7 +4291,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="38"/>
@@ -5691,7 +5718,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="38"/>
@@ -5711,7 +5738,7 @@
       <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="38"/>
@@ -5793,7 +5820,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="40" t="s">
         <v>126</v>
       </c>
       <c r="B9" s="38"/>
@@ -6962,7 +6989,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="38"/>
@@ -6982,7 +7009,7 @@
       <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="38"/>
@@ -7064,7 +7091,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="40" t="s">
         <v>148</v>
       </c>
       <c r="B9" s="38"/>
@@ -8315,7 +8342,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="38"/>
@@ -8337,7 +8364,7 @@
       <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="38"/>
@@ -8359,7 +8386,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="40" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="38"/>
@@ -8428,7 +8455,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="38"/>
@@ -8468,7 +8495,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="40" t="s">
         <v>181</v>
       </c>
       <c r="B17" s="38"/>
@@ -8523,7 +8550,7 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="40" t="s">
         <v>194</v>
       </c>
       <c r="B25" s="38"/>
@@ -9568,7 +9595,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="38"/>
@@ -9592,7 +9619,7 @@
       <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="38"/>
@@ -9644,7 +9671,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="40" t="s">
         <v>212</v>
       </c>
       <c r="B9" s="38"/>
@@ -10002,7 +10029,7 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="40" t="s">
         <v>244</v>
       </c>
       <c r="B25" s="38"/>
@@ -11107,7 +11134,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>246</v>
       </c>
       <c r="B1" s="38"/>
@@ -12748,7 +12775,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>297</v>
       </c>
       <c r="B1" s="38"/>
@@ -13898,7 +13925,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>87</v>
       </c>
       <c r="B1" s="38"/>
@@ -13922,7 +13949,7 @@
       <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>316</v>
       </c>
       <c r="B3" s="38"/>
@@ -14036,7 +14063,9 @@
       <c r="D7" s="13">
         <v>1</v>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="24" t="s">
+        <v>366</v>
+      </c>
       <c r="F7" s="13">
         <v>2</v>
       </c>
@@ -14083,7 +14112,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="40" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="38"/>
@@ -14245,14 +14274,14 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="40" t="s">
         <v>335</v>
       </c>
       <c r="B15" s="38"/>
       <c r="C15" s="38"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="40" t="s">
         <v>336</v>
       </c>
       <c r="B16" s="38"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5199EE23-8AA3-4944-8666-C21C9A0FC70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671E6507-2678-441B-98F5-342F6569AD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671E6507-2678-441B-98F5-342F6569AD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4484BCB6-023B-4FE9-B058-9D5B629C7874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="366">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -709,9 +709,6 @@
   </si>
   <si>
     <t>NADEC</t>
-  </si>
-  <si>
-    <t>Current dashboard item</t>
   </si>
   <si>
     <t>Feb</t>
@@ -1449,6 +1446,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1458,9 +1458,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1775,24 +1772,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1825,12 +1822,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -2924,41 +2921,41 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3963,32 +3960,32 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>218</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>38</v>
@@ -3996,30 +3993,30 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E5" s="32">
         <v>500000</v>
       </c>
       <c r="G5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E6" s="32">
         <v>500000</v>
@@ -4027,30 +4024,30 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E7" s="32">
         <v>500000</v>
       </c>
       <c r="G7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E8" s="32">
         <v>500000</v>
@@ -4058,13 +4055,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E9" s="32">
         <v>700000</v>
@@ -4072,13 +4069,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E10" s="32">
         <v>200000</v>
@@ -4086,13 +4083,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E11" s="32">
         <v>100000</v>
@@ -4100,13 +4097,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E12" s="32">
         <v>100000</v>
@@ -4114,13 +4111,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E13" s="32">
         <v>100000</v>
@@ -4128,13 +4125,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E14" s="32">
         <v>500000</v>
@@ -4142,120 +4139,120 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B15" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E15" s="32">
         <v>500000</v>
       </c>
       <c r="G15" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E16" s="32">
         <v>400000</v>
       </c>
       <c r="G16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B17" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E17" s="32">
         <v>500000</v>
       </c>
       <c r="G17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B18" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E18" s="32">
         <v>700000</v>
       </c>
       <c r="G18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>349</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>366</v>
+        <v>348</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>365</v>
       </c>
       <c r="G21" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>221</v>
@@ -4263,13 +4260,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -4291,14 +4288,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5718,32 +5715,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -5820,14 +5817,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -6989,32 +6986,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -7091,14 +7088,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -8342,32 +8339,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="38"/>
+      <c r="B3" s="39"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -8386,10 +8383,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="39"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -8455,11 +8452,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -8495,10 +8492,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="38"/>
+      <c r="B17" s="39"/>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8550,10 +8547,10 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="38"/>
+      <c r="B25" s="39"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9595,35 +9592,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -9671,13 +9668,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -9728,13 +9725,11 @@
       <c r="H11" s="22">
         <v>500000</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B12" s="13">
         <v>0</v>
@@ -9750,18 +9745,16 @@
         <v>128</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H12" s="22">
         <v>500000</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B13" s="13">
         <v>0</v>
@@ -9777,18 +9770,16 @@
         <v>128</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H13" s="22">
         <v>350000</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B14" s="13">
         <v>0</v>
@@ -9804,18 +9795,16 @@
         <v>129</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H14" s="22">
         <v>330000</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B15" s="13">
         <v>100000</v>
@@ -9831,18 +9820,16 @@
         <v>129</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H15" s="22">
         <v>220000</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="13">
         <v>185000</v>
@@ -9858,18 +9845,16 @@
         <v>129</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H16" s="22">
         <v>70000</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B17" s="13">
         <v>136125</v>
@@ -9885,18 +9870,16 @@
         <v>130</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H17" s="22">
         <v>50000</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B18" s="13">
         <v>170156</v>
@@ -9912,18 +9895,16 @@
         <v>130</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H18" s="22">
         <v>45000</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B19" s="13">
         <v>331064</v>
@@ -9939,18 +9920,16 @@
         <v>130</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H19" s="22">
         <v>30000</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B20" s="13">
         <v>276963</v>
@@ -9966,7 +9945,7 @@
         <v>131</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H20" s="21">
         <f>SUM(H11:H19)</f>
@@ -9975,7 +9954,7 @@
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B21" s="13">
         <v>330051</v>
@@ -9993,7 +9972,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B22" s="13">
         <v>299067</v>
@@ -10011,7 +9990,7 @@
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" s="14">
         <f>SUM(B11:B22)</f>
@@ -10029,14 +10008,14 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
+      <c r="A25" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -10110,7 +10089,7 @@
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B29" s="14">
         <f>B27+B28</f>
@@ -11134,53 +11113,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>38</v>
@@ -11188,16 +11167,16 @@
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>257</v>
       </c>
       <c r="E4" s="13">
         <v>30000</v>
@@ -11210,24 +11189,24 @@
         <v>28500</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>261</v>
       </c>
       <c r="E5" s="13">
         <v>75000</v>
@@ -11240,24 +11219,24 @@
         <v>75000</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>263</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="23">
@@ -11268,24 +11247,24 @@
         <v/>
       </c>
       <c r="H6" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="E7" s="13">
         <v>500000</v>
@@ -11298,24 +11277,24 @@
         <v>400000</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>268</v>
-      </c>
       <c r="C8" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E8" s="13">
         <v>20000</v>
@@ -11328,24 +11307,24 @@
         <v>20000</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E9" s="13">
         <v>500000</v>
@@ -11358,24 +11337,24 @@
         <v>300000</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>274</v>
       </c>
       <c r="E10" s="13">
         <v>1000000</v>
@@ -11388,24 +11367,24 @@
         <v>600000</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="C11" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="23">
@@ -11415,24 +11394,24 @@
         <v>50000</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>278</v>
-      </c>
       <c r="C12" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="23">
@@ -11442,24 +11421,24 @@
         <v>50000</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>280</v>
-      </c>
       <c r="C13" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="23">
@@ -11469,24 +11448,24 @@
         <v>50000</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E14" s="13">
         <v>100000</v>
@@ -11499,10 +11478,10 @@
         <v>50000</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -11510,13 +11489,13 @@
         <v>221</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>285</v>
-      </c>
       <c r="D15" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E15" s="13">
         <v>500000</v>
@@ -11529,24 +11508,24 @@
         <v>250000</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>257</v>
       </c>
       <c r="E16" s="13">
         <v>90000</v>
@@ -11559,24 +11538,24 @@
         <v>45000</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="C17" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="23">
@@ -11587,24 +11566,24 @@
         <v/>
       </c>
       <c r="H17" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E18" s="13">
         <v>195000</v>
@@ -11617,24 +11596,24 @@
         <v>78000</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>291</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>292</v>
       </c>
       <c r="E19" s="13">
         <v>100000</v>
@@ -11647,24 +11626,24 @@
         <v>30000</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>274</v>
       </c>
       <c r="E20" s="13">
         <v>45000</v>
@@ -11677,24 +11656,24 @@
         <v>27000</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E21" s="13">
         <v>30000</v>
@@ -11707,24 +11686,24 @@
         <v>30000</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E22" s="13">
         <v>140000</v>
@@ -11737,24 +11716,24 @@
         <v>70000</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>295</v>
-      </c>
       <c r="C23" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E23" s="13">
         <v>100000</v>
@@ -11767,10 +11746,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12775,42 +12754,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-    </row>
-    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>302</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>303</v>
       </c>
       <c r="C4" s="23">
         <v>1</v>
@@ -12818,10 +12797,10 @@
     </row>
     <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
@@ -12829,10 +12808,10 @@
     </row>
     <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>305</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>306</v>
       </c>
       <c r="C6" s="23">
         <v>0.5</v>
@@ -12840,10 +12819,10 @@
     </row>
     <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C7" s="23">
         <v>0.5</v>
@@ -12851,10 +12830,10 @@
     </row>
     <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C8" s="23">
         <v>0.5</v>
@@ -12862,10 +12841,10 @@
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C9" s="23">
         <v>0.4</v>
@@ -12873,10 +12852,10 @@
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C10" s="23">
         <v>0.3</v>
@@ -12884,10 +12863,10 @@
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>311</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>312</v>
       </c>
       <c r="C11" s="23">
         <v>0.3</v>
@@ -12895,10 +12874,10 @@
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C12" s="23">
         <v>0.3</v>
@@ -12906,10 +12885,10 @@
     </row>
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C13" s="23">
         <v>0.2</v>
@@ -13925,64 +13904,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+    </row>
+    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="41" t="s">
         <v>315</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-    </row>
-    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
-        <v>316</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="18" t="s">
         <v>321</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>322</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>116</v>
@@ -13990,7 +13969,7 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B5" s="13">
         <v>9</v>
@@ -14002,7 +13981,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F5" s="13">
         <v>7</v>
@@ -14015,7 +13994,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14045,12 +14024,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Submitted")</f>
@@ -14064,7 +14043,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F7" s="13">
         <v>2</v>
@@ -14077,12 +14056,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B8" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Won")</f>
@@ -14108,17 +14087,17 @@
         <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
       <c r="G9" s="26">
         <v>0.6</v>
       </c>
@@ -14127,21 +14106,21 @@
         <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>206</v>
@@ -14154,12 +14133,12 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B11" s="14">
         <f t="shared" ref="B11:C14" si="0">B5</f>
@@ -14173,7 +14152,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G11" s="26">
         <v>0.8</v>
@@ -14183,12 +14162,12 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
@@ -14203,7 +14182,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G12" s="26">
         <v>0.85</v>
@@ -14213,12 +14192,12 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B13" s="14">
         <f t="shared" si="0"/>
@@ -14230,7 +14209,7 @@
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G13" s="26">
         <v>0.95</v>
@@ -14240,12 +14219,12 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B14" s="14">
         <f t="shared" si="0"/>
@@ -14260,7 +14239,7 @@
         <v>0.11764705882352941</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G14" s="26">
         <v>1</v>
@@ -14270,29 +14249,29 @@
         <v>3</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+    </row>
+    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="41" t="s">
         <v>335</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-    </row>
-    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="40" t="s">
+      <c r="B16" s="39"/>
+      <c r="G16" s="18" t="s">
         <v>336</v>
-      </c>
-      <c r="B16" s="38"/>
-      <c r="G16" s="18" t="s">
-        <v>337</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>218</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14300,17 +14279,15 @@
         <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>264</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H17" s="27"/>
       <c r="I17" s="21">
         <f>SUMIF(Sales_Raw_Opportunities!A:A,H17,Sales_Raw_Opportunities!E:E)</f>
-        <v>1590000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14359,12 +14336,12 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4484BCB6-023B-4FE9-B058-9D5B629C7874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B52FD6-FD26-48A7-8B59-97928A0A08D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1449,14 +1449,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1772,7 +1772,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -1782,7 +1782,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -1822,7 +1822,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="38" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="39"/>
@@ -4288,7 +4288,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="39"/>
@@ -5715,7 +5715,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="39"/>
@@ -5725,7 +5725,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>112</v>
       </c>
       <c r="B2" s="39"/>
@@ -5735,7 +5735,7 @@
       <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="38" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="39"/>
@@ -5817,7 +5817,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="38" t="s">
         <v>126</v>
       </c>
       <c r="B9" s="39"/>
@@ -6986,7 +6986,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="39"/>
@@ -6996,7 +6996,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>139</v>
       </c>
       <c r="B2" s="39"/>
@@ -7006,7 +7006,7 @@
       <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="38" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="39"/>
@@ -7088,7 +7088,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="38" t="s">
         <v>148</v>
       </c>
       <c r="B9" s="39"/>
@@ -8339,7 +8339,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="39"/>
@@ -8350,7 +8350,7 @@
       <c r="G1" s="39"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>154</v>
       </c>
       <c r="B2" s="39"/>
@@ -8361,7 +8361,7 @@
       <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="38" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="39"/>
@@ -8383,7 +8383,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="38" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="39"/>
@@ -8452,7 +8452,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="38" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="39"/>
@@ -8492,7 +8492,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="38" t="s">
         <v>181</v>
       </c>
       <c r="B17" s="39"/>
@@ -8547,7 +8547,7 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="38" t="s">
         <v>194</v>
       </c>
       <c r="B25" s="39"/>
@@ -9592,7 +9592,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="39"/>
@@ -9604,7 +9604,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>204</v>
       </c>
       <c r="B2" s="39"/>
@@ -9616,7 +9616,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="38" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="39"/>
@@ -9668,7 +9668,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="38" t="s">
         <v>212</v>
       </c>
       <c r="B9" s="39"/>
@@ -10008,7 +10008,7 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="38" t="s">
         <v>243</v>
       </c>
       <c r="B25" s="39"/>
@@ -11113,7 +11113,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>245</v>
       </c>
       <c r="B1" s="39"/>
@@ -11125,7 +11125,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>246</v>
       </c>
       <c r="B2" s="39"/>
@@ -12754,7 +12754,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>296</v>
       </c>
       <c r="B1" s="39"/>
@@ -12764,7 +12764,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>297</v>
       </c>
       <c r="B2" s="39"/>
@@ -13904,7 +13904,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>87</v>
       </c>
       <c r="B1" s="39"/>
@@ -13916,7 +13916,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>314</v>
       </c>
       <c r="B2" s="39"/>
@@ -13928,7 +13928,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="38" t="s">
         <v>315</v>
       </c>
       <c r="B3" s="39"/>
@@ -14091,7 +14091,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="38" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="39"/>
@@ -14253,14 +14253,14 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="38" t="s">
         <v>334</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="38" t="s">
         <v>335</v>
       </c>
       <c r="B16" s="39"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B52FD6-FD26-48A7-8B59-97928A0A08D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F450D68-2FF7-433B-B540-0EF08BED118F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="361">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1092,22 +1092,7 @@
     <t>This Month</t>
   </si>
   <si>
-    <t>Add lead rows here if you want the dashboard to show client-level detail for leads.</t>
-  </si>
-  <si>
     <t>This Week</t>
-  </si>
-  <si>
-    <t>Weekly detail is manual because the current raw opportunity source does not contain exact dates.</t>
-  </si>
-  <si>
-    <t>Add weekly active proposal detail here if needed.</t>
-  </si>
-  <si>
-    <t>Add weekly submitted detail here if needed.</t>
-  </si>
-  <si>
-    <t>Add weekly won detail here if needed.</t>
   </si>
   <si>
     <t xml:space="preserve">Nadec </t>
@@ -1449,11 +1434,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1782,7 +1767,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -1822,7 +1807,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="40" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="39"/>
@@ -4004,9 +3989,6 @@
       <c r="E5" s="32">
         <v>500000</v>
       </c>
-      <c r="G5" t="s">
-        <v>349</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
@@ -4016,7 +3998,7 @@
         <v>348</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E6" s="32">
         <v>500000</v>
@@ -4027,16 +4009,13 @@
         <v>341</v>
       </c>
       <c r="B7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E7" s="32">
         <v>500000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -4044,10 +4023,10 @@
         <v>341</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E8" s="32">
         <v>500000</v>
@@ -4058,10 +4037,10 @@
         <v>341</v>
       </c>
       <c r="B9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E9" s="32">
         <v>700000</v>
@@ -4072,10 +4051,10 @@
         <v>341</v>
       </c>
       <c r="B10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E10" s="32">
         <v>200000</v>
@@ -4086,10 +4065,10 @@
         <v>341</v>
       </c>
       <c r="B11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E11" s="32">
         <v>100000</v>
@@ -4100,10 +4079,10 @@
         <v>341</v>
       </c>
       <c r="B12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E12" s="32">
         <v>100000</v>
@@ -4114,10 +4093,10 @@
         <v>341</v>
       </c>
       <c r="B13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E13" s="32">
         <v>100000</v>
@@ -4128,10 +4107,10 @@
         <v>341</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E14" s="32">
         <v>500000</v>
@@ -4142,16 +4121,13 @@
         <v>342</v>
       </c>
       <c r="B15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C15" s="35" t="s">
         <v>223</v>
       </c>
       <c r="E15" s="32">
         <v>500000</v>
-      </c>
-      <c r="G15" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -4159,7 +4135,7 @@
         <v>342</v>
       </c>
       <c r="B16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>288</v>
@@ -4167,70 +4143,58 @@
       <c r="E16" s="32">
         <v>400000</v>
       </c>
-      <c r="G16" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>342</v>
       </c>
       <c r="B17" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E17" s="32">
         <v>500000</v>
       </c>
-      <c r="G17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>342</v>
       </c>
       <c r="B18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E18" s="32">
         <v>700000</v>
       </c>
-      <c r="G18" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C19" t="s">
-        <v>364</v>
-      </c>
-      <c r="G19" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C20" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>249</v>
       </c>
@@ -4241,13 +4205,10 @@
         <v>280</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="G21" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>249</v>
       </c>
@@ -4258,15 +4219,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>268</v>
       </c>
       <c r="B23" t="s">
-        <v>350</v>
-      </c>
-      <c r="G23" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -5725,7 +5683,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>112</v>
       </c>
       <c r="B2" s="39"/>
@@ -5735,7 +5693,7 @@
       <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="40" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="39"/>
@@ -5817,7 +5775,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="40" t="s">
         <v>126</v>
       </c>
       <c r="B9" s="39"/>
@@ -6996,7 +6954,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>139</v>
       </c>
       <c r="B2" s="39"/>
@@ -7006,7 +6964,7 @@
       <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="40" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="39"/>
@@ -7088,7 +7046,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="40" t="s">
         <v>148</v>
       </c>
       <c r="B9" s="39"/>
@@ -8350,7 +8308,7 @@
       <c r="G1" s="39"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>154</v>
       </c>
       <c r="B2" s="39"/>
@@ -8361,7 +8319,7 @@
       <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="40" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="39"/>
@@ -8383,7 +8341,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="40" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="39"/>
@@ -8452,7 +8410,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="39"/>
@@ -8492,7 +8450,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="40" t="s">
         <v>181</v>
       </c>
       <c r="B17" s="39"/>
@@ -8547,7 +8505,7 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="40" t="s">
         <v>194</v>
       </c>
       <c r="B25" s="39"/>
@@ -9604,7 +9562,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>204</v>
       </c>
       <c r="B2" s="39"/>
@@ -9616,7 +9574,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="40" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="39"/>
@@ -9668,7 +9626,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="40" t="s">
         <v>212</v>
       </c>
       <c r="B9" s="39"/>
@@ -10008,7 +9966,7 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="40" t="s">
         <v>243</v>
       </c>
       <c r="B25" s="39"/>
@@ -11125,7 +11083,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>246</v>
       </c>
       <c r="B2" s="39"/>
@@ -12764,7 +12722,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>297</v>
       </c>
       <c r="B2" s="39"/>
@@ -13916,7 +13874,7 @@
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>314</v>
       </c>
       <c r="B2" s="39"/>
@@ -13928,7 +13886,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="40" t="s">
         <v>315</v>
       </c>
       <c r="B3" s="39"/>
@@ -14043,7 +14001,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F7" s="13">
         <v>2</v>
@@ -14091,7 +14049,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="40" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="39"/>
@@ -14253,14 +14211,14 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="40" t="s">
         <v>334</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="40" t="s">
         <v>335</v>
       </c>
       <c r="B16" s="39"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F450D68-2FF7-433B-B540-0EF08BED118F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE713214-00DE-4168-8F08-3800760C0288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="343">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -819,15 +819,6 @@
     <t>Imported from dashboard</t>
   </si>
   <si>
-    <t>SIDF</t>
-  </si>
-  <si>
-    <t>ESG Workshop</t>
-  </si>
-  <si>
-    <t>Sep 2025</t>
-  </si>
-  <si>
     <t>KSA Sustainability Champions</t>
   </si>
   <si>
@@ -837,18 +828,6 @@
     <t>Tadawul Group</t>
   </si>
   <si>
-    <t>GDP ESG Workshop</t>
-  </si>
-  <si>
-    <t>Oct 2025</t>
-  </si>
-  <si>
-    <t>Center For Gov.</t>
-  </si>
-  <si>
-    <t>ESG Course Development</t>
-  </si>
-  <si>
     <t>Won</t>
   </si>
   <si>
@@ -861,30 +840,6 @@
     <t>Feb 2026</t>
   </si>
   <si>
-    <t>ESG &amp; Corp. Governance</t>
-  </si>
-  <si>
-    <t>Aug 2025</t>
-  </si>
-  <si>
-    <t>KACST</t>
-  </si>
-  <si>
-    <t>Elevating KACST's ESG Story</t>
-  </si>
-  <si>
-    <t>KAUST</t>
-  </si>
-  <si>
-    <t>From Lab to Kingdom</t>
-  </si>
-  <si>
-    <t>King Saud Univ.</t>
-  </si>
-  <si>
-    <t>Future Proofing KSU Graduates</t>
-  </si>
-  <si>
     <t>Middle Beast</t>
   </si>
   <si>
@@ -910,15 +865,6 @@
   </si>
   <si>
     <t>ITQAN</t>
-  </si>
-  <si>
-    <t>Obeikan</t>
-  </si>
-  <si>
-    <t>RPI ESG Workshop</t>
-  </si>
-  <si>
-    <t>Nov 2025</t>
   </si>
   <si>
     <t>Tadawul ESG Course</t>
@@ -1523,7 +1469,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I12">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Client"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Opportunity"/>
@@ -2906,18 +2852,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -2925,22 +2871,22 @@
         <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3945,12 +3891,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3958,7 +3904,7 @@
         <v>253</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>218</v>
@@ -3970,7 +3916,7 @@
         <v>250</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>38</v>
@@ -3978,10 +3924,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>223</v>
@@ -3992,13 +3938,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="E6" s="32">
         <v>500000</v>
@@ -4006,13 +3952,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="E7" s="32">
         <v>500000</v>
@@ -4020,13 +3966,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="E8" s="32">
         <v>500000</v>
@@ -4034,13 +3980,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B9" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="E9" s="32">
         <v>700000</v>
@@ -4048,13 +3994,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B10" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="E10" s="32">
         <v>200000</v>
@@ -4062,13 +4008,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B11" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="E11" s="32">
         <v>100000</v>
@@ -4076,13 +4022,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B12" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="E12" s="32">
         <v>100000</v>
@@ -4090,13 +4036,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="E13" s="32">
         <v>100000</v>
@@ -4104,13 +4050,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B14" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="E14" s="32">
         <v>500000</v>
@@ -4118,10 +4064,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B15" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C15" s="35" t="s">
         <v>223</v>
@@ -4132,13 +4078,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B16" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="E16" s="32">
         <v>400000</v>
@@ -4146,13 +4092,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B17" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="E17" s="32">
         <v>500000</v>
@@ -4160,13 +4106,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B18" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="E18" s="32">
         <v>700000</v>
@@ -4177,10 +4123,13 @@
         <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C19" t="s">
-        <v>359</v>
+        <v>341</v>
+      </c>
+      <c r="E19" s="32">
+        <v>20000</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -4188,10 +4137,13 @@
         <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C20" t="s">
         <v>223</v>
+      </c>
+      <c r="E20" s="32">
+        <v>500000</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -4199,13 +4151,13 @@
         <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -4213,7 +4165,7 @@
         <v>249</v>
       </c>
       <c r="B22" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>221</v>
@@ -4221,10 +4173,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -11056,7 +11008,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:I990"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -11143,7 +11095,7 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="14">
-        <f t="shared" ref="G4:G10" si="0">IF(AND(E4&lt;&gt;0,NOT(ISBLANK(E4)),NOT(ISBLANK(F4))),E4*F4,"")</f>
+        <f t="shared" ref="G4:G6" si="0">IF(AND(E4&lt;&gt;0,NOT(ISBLANK(E4)),NOT(ISBLANK(F4))),E4*F4,"")</f>
         <v>28500</v>
       </c>
       <c r="H4" s="24" t="s">
@@ -11155,26 +11107,26 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>259</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E5" s="13">
-        <v>75000</v>
+        <v>500000</v>
       </c>
       <c r="F5" s="23">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G5" s="14">
         <f t="shared" si="0"/>
-        <v>75000</v>
+        <v>425000</v>
       </c>
       <c r="H5" s="24" t="s">
         <v>249</v>
@@ -11185,24 +11137,26 @@
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="E6" s="13"/>
+        <v>264</v>
+      </c>
+      <c r="E6" s="13">
+        <v>500000</v>
+      </c>
       <c r="F6" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="G6" s="14" t="str">
+        <v>0.6</v>
+      </c>
+      <c r="G6" s="14">
         <f t="shared" si="0"/>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="H6" s="24" t="s">
         <v>249</v>
@@ -11213,26 +11167,26 @@
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E7" s="13">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="F7" s="23">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="14">
-        <f t="shared" si="0"/>
-        <v>400000</v>
+        <f t="shared" ref="G7:G12" si="1">IF(AND(E7&lt;&gt;0,NOT(ISBLANK(E7)),NOT(ISBLANK(F7))),E7*F7,"")</f>
+        <v>50000</v>
       </c>
       <c r="H7" s="24" t="s">
         <v>249</v>
@@ -11243,29 +11197,29 @@
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E8" s="13">
-        <v>20000</v>
+        <v>500000</v>
       </c>
       <c r="F8" s="23">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="14">
-        <f t="shared" si="0"/>
-        <v>20000</v>
+        <f t="shared" si="1"/>
+        <v>250000</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>257</v>
@@ -11273,7 +11227,7 @@
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>270</v>
@@ -11282,17 +11236,17 @@
         <v>255</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="E9" s="13">
-        <v>500000</v>
+        <v>90000</v>
       </c>
       <c r="F9" s="23">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="14">
-        <f t="shared" si="0"/>
-        <v>300000</v>
+        <f t="shared" si="1"/>
+        <v>45000</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>249</v>
@@ -11303,7 +11257,7 @@
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>272</v>
@@ -11312,17 +11266,17 @@
         <v>255</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E10" s="13">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="F10" s="23">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="14">
-        <f t="shared" si="0"/>
-        <v>600000</v>
+        <f t="shared" si="1"/>
+        <v>50000</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>249</v>
@@ -11331,394 +11285,86 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>275</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E11" s="13"/>
+        <v>264</v>
+      </c>
+      <c r="E11" s="13">
+        <v>30000</v>
+      </c>
       <c r="F11" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="14">
-        <v>50000</v>
+        <f t="shared" si="1"/>
+        <v>30000</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E12" s="13"/>
+        <v>259</v>
+      </c>
+      <c r="E12" s="13">
+        <v>100000</v>
+      </c>
       <c r="F12" s="23">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
-        <v>50000</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="14">
-        <v>50000</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="E14" s="13">
-        <v>100000</v>
-      </c>
-      <c r="F14" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" ref="G14:G23" si="1">IF(AND(E14&lt;&gt;0,NOT(ISBLANK(E14)),NOT(ISBLANK(F14))),E14*F14,"")</f>
-        <v>50000</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E15" s="13">
-        <v>500000</v>
-      </c>
-      <c r="F15" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="14">
-        <f t="shared" si="1"/>
-        <v>250000</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16" s="13">
-        <v>90000</v>
-      </c>
-      <c r="F16" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="14">
-        <f t="shared" si="1"/>
-        <v>45000</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E18" s="13">
-        <v>195000</v>
-      </c>
-      <c r="F18" s="23">
-        <v>0.4</v>
-      </c>
-      <c r="G18" s="14">
-        <f t="shared" si="1"/>
-        <v>78000</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E19" s="13">
-        <v>100000</v>
-      </c>
-      <c r="F19" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="14">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="E20" s="13">
-        <v>45000</v>
-      </c>
-      <c r="F20" s="23">
-        <v>0.6</v>
-      </c>
-      <c r="G20" s="14">
-        <f t="shared" si="1"/>
-        <v>27000</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E21" s="13">
-        <v>30000</v>
-      </c>
-      <c r="F21" s="23">
-        <v>1</v>
-      </c>
-      <c r="G21" s="14">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E22" s="13">
-        <v>140000</v>
-      </c>
-      <c r="F22" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="14">
-        <f t="shared" si="1"/>
-        <v>70000</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="E23" s="13">
-        <v>100000</v>
-      </c>
-      <c r="F23" s="23">
-        <v>0</v>
-      </c>
-      <c r="G23" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12677,17 +12323,6 @@
     <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -12713,7 +12348,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -12723,7 +12358,7 @@
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -12733,21 +12368,21 @@
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C4" s="23">
         <v>1</v>
@@ -12755,10 +12390,10 @@
     </row>
     <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
@@ -12766,10 +12401,10 @@
     </row>
     <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C6" s="23">
         <v>0.5</v>
@@ -12777,10 +12412,10 @@
     </row>
     <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C7" s="23">
         <v>0.5</v>
@@ -12788,10 +12423,10 @@
     </row>
     <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C8" s="23">
         <v>0.5</v>
@@ -12799,10 +12434,10 @@
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C9" s="23">
         <v>0.4</v>
@@ -12810,10 +12445,10 @@
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C10" s="23">
         <v>0.3</v>
@@ -12821,10 +12456,10 @@
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="C11" s="23">
         <v>0.3</v>
@@ -12832,10 +12467,10 @@
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="C12" s="23">
         <v>0.3</v>
@@ -12843,10 +12478,10 @@
     </row>
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="C13" s="23">
         <v>0.2</v>
@@ -13875,7 +13510,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -13887,7 +13522,7 @@
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="40" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -13901,25 +13536,25 @@
         <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>116</v>
@@ -13927,7 +13562,7 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="B5" s="13">
         <v>9</v>
@@ -13939,7 +13574,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="F5" s="13">
         <v>7</v>
@@ -13952,7 +13587,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13979,29 +13614,29 @@
       </c>
       <c r="H6" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Submitted")</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C7" s="13">
         <f>SUMIF(Sales_Raw_Opportunities!H:H,"Submitted",Sales_Raw_Opportunities!E:E)</f>
-        <v>3275000</v>
+        <v>1820000</v>
       </c>
       <c r="D7" s="13">
         <v>1</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="F7" s="13">
         <v>2</v>
@@ -14011,23 +13646,23 @@
       </c>
       <c r="H7" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="B8" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Won")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="13">
         <f>SUMIF(Sales_Raw_Opportunities!H:H,"Won",Sales_Raw_Opportunities!E:E)</f>
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="D8" s="13">
         <f>COUNTIFS(Sales_Raw_Opportunities!H:H,"Won",Sales_Raw_Opportunities!D:D,"Apr 2026")</f>
@@ -14042,10 +13677,10 @@
       </c>
       <c r="H8" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G8)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14061,10 +13696,10 @@
       </c>
       <c r="H9" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G9)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14072,13 +13707,13 @@
         <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>206</v>
@@ -14091,12 +13726,12 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="B11" s="14">
         <f t="shared" ref="B11:C14" si="0">B5</f>
@@ -14110,22 +13745,22 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="G11" s="26">
         <v>0.8</v>
       </c>
       <c r="H11" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G11)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
@@ -14140,7 +13775,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="G12" s="26">
         <v>0.85</v>
@@ -14150,24 +13785,24 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="B13" s="14">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C13" s="14">
         <f t="shared" si="0"/>
-        <v>3275000</v>
+        <v>1820000</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G13" s="26">
         <v>0.95</v>
@@ -14177,59 +13812,59 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="B14" s="14">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="14">
         <f t="shared" si="0"/>
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="D14" s="15">
         <f>IFERROR(B14/B13,0)</f>
-        <v>0.11764705882352941</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="G14" s="26">
         <v>1</v>
       </c>
       <c r="H14" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G14)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="B16" s="39"/>
       <c r="G16" s="18" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>218</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14237,7 +13872,7 @@
         <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -14294,12 +13929,12 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE713214-00DE-4168-8F08-3800760C0288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5D0A8D-8053-4F12-BE36-84D4BF51B5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="343">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1084,11 +1084,18 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1287,109 +1294,111 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1703,7 +1712,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -1753,7 +1762,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="41" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="39"/>
@@ -4178,6 +4187,12 @@
       <c r="B23" t="s">
         <v>331</v>
       </c>
+      <c r="C23" s="43" t="s">
+        <v>341</v>
+      </c>
+      <c r="E23" s="42">
+        <v>20000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4198,7 +4213,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="39"/>
@@ -5625,7 +5640,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="39"/>
@@ -5645,7 +5660,7 @@
       <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="39"/>
@@ -5727,7 +5742,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>126</v>
       </c>
       <c r="B9" s="39"/>
@@ -6896,7 +6911,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="39"/>
@@ -6916,7 +6931,7 @@
       <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="39"/>
@@ -6998,7 +7013,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>148</v>
       </c>
       <c r="B9" s="39"/>
@@ -8249,7 +8264,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="39"/>
@@ -8271,7 +8286,7 @@
       <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="39"/>
@@ -8293,7 +8308,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="41" t="s">
         <v>59</v>
       </c>
       <c r="B7" s="39"/>
@@ -8362,7 +8377,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="41" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="39"/>
@@ -8402,7 +8417,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="41" t="s">
         <v>181</v>
       </c>
       <c r="B17" s="39"/>
@@ -8457,7 +8472,7 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="41" t="s">
         <v>194</v>
       </c>
       <c r="B25" s="39"/>
@@ -9502,7 +9517,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="39"/>
@@ -9526,7 +9541,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="39"/>
@@ -9578,7 +9593,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>212</v>
       </c>
       <c r="B9" s="39"/>
@@ -9918,7 +9933,7 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
+      <c r="A25" s="41" t="s">
         <v>243</v>
       </c>
       <c r="B25" s="39"/>
@@ -11023,7 +11038,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>245</v>
       </c>
       <c r="B1" s="39"/>
@@ -12347,7 +12362,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>278</v>
       </c>
       <c r="B1" s="39"/>
@@ -13497,7 +13512,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>87</v>
       </c>
       <c r="B1" s="39"/>
@@ -13521,7 +13536,7 @@
       <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="41" t="s">
         <v>297</v>
       </c>
       <c r="B3" s="39"/>
@@ -13684,7 +13699,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="41" t="s">
         <v>91</v>
       </c>
       <c r="B9" s="39"/>
@@ -13846,14 +13861,14 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="41" t="s">
         <v>316</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="41" t="s">
         <v>317</v>
       </c>
       <c r="B16" s="39"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5D0A8D-8053-4F12-BE36-84D4BF51B5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031A6121-37D8-47AB-B3A6-82DCE96D55DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="341">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -816,9 +816,6 @@
     <t>Jan 2026</t>
   </si>
   <si>
-    <t>Imported from dashboard</t>
-  </si>
-  <si>
     <t>KSA Sustainability Champions</t>
   </si>
   <si>
@@ -1033,9 +1030,6 @@
   </si>
   <si>
     <t>Owner</t>
-  </si>
-  <si>
-    <t>This Month</t>
   </si>
   <si>
     <t>This Week</t>
@@ -2861,18 +2855,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -2880,22 +2874,22 @@
         <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3900,12 +3894,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3913,7 +3907,7 @@
         <v>253</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>218</v>
@@ -3925,7 +3919,7 @@
         <v>250</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>38</v>
@@ -3933,10 +3927,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>223</v>
@@ -3947,13 +3941,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="31" t="s">
         <v>330</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>332</v>
       </c>
       <c r="E6" s="32">
         <v>500000</v>
@@ -3961,13 +3955,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E7" s="32">
         <v>500000</v>
@@ -3975,13 +3969,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>331</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>333</v>
       </c>
       <c r="E8" s="32">
         <v>500000</v>
@@ -3989,13 +3983,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E9" s="32">
         <v>700000</v>
@@ -4003,13 +3997,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E10" s="32">
         <v>200000</v>
@@ -4017,13 +4011,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E11" s="32">
         <v>100000</v>
@@ -4031,13 +4025,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E12" s="32">
         <v>100000</v>
@@ -4045,13 +4039,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B13" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E13" s="32">
         <v>100000</v>
@@ -4059,13 +4053,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B14" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E14" s="32">
         <v>500000</v>
@@ -4073,10 +4067,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C15" s="35" t="s">
         <v>223</v>
@@ -4087,13 +4081,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B16" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E16" s="32">
         <v>400000</v>
@@ -4101,13 +4095,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B17" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E17" s="32">
         <v>500000</v>
@@ -4115,13 +4109,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B18" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E18" s="32">
         <v>700000</v>
@@ -4132,10 +4126,10 @@
         <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E19" s="32">
         <v>20000</v>
@@ -4146,7 +4140,7 @@
         <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C20" t="s">
         <v>223</v>
@@ -4160,13 +4154,13 @@
         <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -4174,7 +4168,7 @@
         <v>249</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>221</v>
@@ -4182,13 +4176,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E23" s="42">
         <v>20000</v>
@@ -11116,22 +11110,20 @@
       <c r="H4" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="I4" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>223</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E5" s="13">
         <v>500000</v>
@@ -11146,22 +11138,20 @@
       <c r="H5" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>263</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E6" s="13">
         <v>500000</v>
@@ -11176,22 +11166,20 @@
       <c r="H6" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>266</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E7" s="13">
         <v>100000</v>
@@ -11206,22 +11194,20 @@
       <c r="H7" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>221</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>269</v>
-      </c>
       <c r="D8" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E8" s="13">
         <v>500000</v>
@@ -11236,16 +11222,14 @@
       <c r="H8" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>255</v>
@@ -11266,22 +11250,20 @@
       <c r="H9" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>272</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E10" s="13">
         <v>100000</v>
@@ -11296,22 +11278,20 @@
       <c r="H10" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>257</v>
-      </c>
+      <c r="I10" s="12"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>237</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E11" s="13">
         <v>30000</v>
@@ -11324,24 +11304,22 @@
         <v>30000</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>257</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>276</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>255</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E12" s="13">
         <v>100000</v>
@@ -11354,11 +11332,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>257</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12363,7 +12339,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -12373,7 +12349,7 @@
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -12383,21 +12359,21 @@
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>283</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>284</v>
       </c>
       <c r="C4" s="23">
         <v>1</v>
@@ -12405,10 +12381,10 @@
     </row>
     <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
@@ -12416,10 +12392,10 @@
     </row>
     <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>286</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>287</v>
       </c>
       <c r="C6" s="23">
         <v>0.5</v>
@@ -12427,10 +12403,10 @@
     </row>
     <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C7" s="23">
         <v>0.5</v>
@@ -12438,10 +12414,10 @@
     </row>
     <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C8" s="23">
         <v>0.5</v>
@@ -12449,10 +12425,10 @@
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="23">
         <v>0.4</v>
@@ -12460,10 +12436,10 @@
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C10" s="23">
         <v>0.3</v>
@@ -12471,10 +12447,10 @@
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>292</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>293</v>
       </c>
       <c r="C11" s="23">
         <v>0.3</v>
@@ -12482,10 +12458,10 @@
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C12" s="23">
         <v>0.3</v>
@@ -12493,10 +12469,10 @@
     </row>
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C13" s="23">
         <v>0.2</v>
@@ -13525,7 +13501,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -13537,7 +13513,7 @@
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="41" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -13551,25 +13527,25 @@
         <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="18" t="s">
         <v>302</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>303</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>116</v>
@@ -13577,7 +13553,7 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B5" s="13">
         <v>9</v>
@@ -13589,7 +13565,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F5" s="13">
         <v>7</v>
@@ -13602,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13632,12 +13608,12 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Submitted")</f>
@@ -13651,7 +13627,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F7" s="13">
         <v>2</v>
@@ -13664,12 +13640,12 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B8" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Won")</f>
@@ -13695,7 +13671,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13714,7 +13690,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13722,13 +13698,13 @@
         <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>206</v>
@@ -13741,12 +13717,12 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B11" s="14">
         <f t="shared" ref="B11:C14" si="0">B5</f>
@@ -13760,7 +13736,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G11" s="26">
         <v>0.8</v>
@@ -13770,12 +13746,12 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
@@ -13790,7 +13766,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G12" s="26">
         <v>0.85</v>
@@ -13800,12 +13776,12 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B13" s="14">
         <f t="shared" si="0"/>
@@ -13817,7 +13793,7 @@
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G13" s="26">
         <v>0.95</v>
@@ -13827,12 +13803,12 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B14" s="14">
         <f t="shared" si="0"/>
@@ -13847,7 +13823,7 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G14" s="26">
         <v>1</v>
@@ -13857,29 +13833,29 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B16" s="39"/>
       <c r="G16" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>218</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13887,7 +13863,7 @@
         <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -13944,12 +13920,12 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031A6121-37D8-47AB-B3A6-82DCE96D55DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CBC625-8416-4926-854B-D46EA857928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1290,7 +1290,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1393,6 +1393,9 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -13556,15 +13559,17 @@
         <v>303</v>
       </c>
       <c r="B5" s="13">
-        <v>9</v>
+        <f>COUNTIF(Sales_Stage_Details!A:A,"Lead")</f>
+        <v>10</v>
       </c>
       <c r="C5" s="13">
+        <f>SUMIF(Sales_Stage_Details!A:A,"Lead",Sales_Stage_Details!E:E)</f>
         <v>3700000</v>
       </c>
       <c r="D5" s="13">
         <v>2</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="44" t="s">
         <v>304</v>
       </c>
       <c r="F5" s="13">
@@ -13586,12 +13591,12 @@
         <v>79</v>
       </c>
       <c r="B6" s="13">
-        <f>COUNTA(Pipeline_Revenue!G11:G19)</f>
-        <v>9</v>
+        <f>COUNTIF(Sales_Stage_Details!A:A,"Active Proposal")</f>
+        <v>4</v>
       </c>
       <c r="C6" s="13">
-        <f>SUM(Pipeline_Revenue!H11:H19)</f>
-        <v>2095000</v>
+        <f>SUMIF(Sales_Stage_Details!A:A,"Active Proposal",Sales_Stage_Details!E:E)</f>
+        <v>2100000</v>
       </c>
       <c r="D6" s="13">
         <v>0</v>
@@ -13616,12 +13621,12 @@
         <v>306</v>
       </c>
       <c r="B7" s="13">
-        <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Submitted")</f>
-        <v>7</v>
+        <f>COUNTIF(Sales_Stage_Details!A:A,"Submitted")</f>
+        <v>4</v>
       </c>
       <c r="C7" s="13">
-        <f>SUMIF(Sales_Raw_Opportunities!H:H,"Submitted",Sales_Raw_Opportunities!E:E)</f>
-        <v>1820000</v>
+        <f>SUMIF(Sales_Stage_Details!A:A,"Submitted",Sales_Stage_Details!E:E)</f>
+        <v>520000</v>
       </c>
       <c r="D7" s="13">
         <v>1</v>
@@ -13725,11 +13730,10 @@
         <v>309</v>
       </c>
       <c r="B11" s="14">
-        <f t="shared" ref="B11:C14" si="0">B5</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B11:C14" si="0">C5</f>
         <v>3700000</v>
       </c>
       <c r="D11" s="15">
@@ -13755,15 +13759,15 @@
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C12" s="14">
         <f t="shared" si="0"/>
-        <v>2095000</v>
+        <v>2100000</v>
       </c>
       <c r="D12" s="15">
         <f>IFERROR(B12/B11,0)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>310</v>
@@ -13785,11 +13789,11 @@
       </c>
       <c r="B13" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C13" s="14">
         <f t="shared" si="0"/>
-        <v>1820000</v>
+        <v>520000</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
@@ -13820,7 +13824,7 @@
       </c>
       <c r="D14" s="15">
         <f>IFERROR(B14/B13,0)</f>
-        <v>0.14285714285714285</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>310</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CBC625-8416-4926-854B-D46EA857928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B53D4E-CFA7-4A7F-920E-0B67A45C7121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="339">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -865,12 +865,6 @@
   </si>
   <si>
     <t>Tadawul ESG Course</t>
-  </si>
-  <si>
-    <t>PIF</t>
-  </si>
-  <si>
-    <t>PIF Offsite Proposal</t>
   </si>
   <si>
     <t>Lost</t>
@@ -1475,7 +1469,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I11">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Client"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Opportunity"/>
@@ -2858,18 +2852,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -2877,7 +2871,7 @@
         <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -2887,12 +2881,12 @@
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3897,12 +3891,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3910,7 +3904,7 @@
         <v>253</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>218</v>
@@ -3922,7 +3916,7 @@
         <v>250</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>38</v>
@@ -3930,10 +3924,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>223</v>
@@ -3944,13 +3938,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E6" s="32">
         <v>500000</v>
@@ -3958,13 +3952,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E7" s="32">
         <v>500000</v>
@@ -3972,13 +3966,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>329</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>331</v>
       </c>
       <c r="E8" s="32">
         <v>500000</v>
@@ -3986,13 +3980,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E9" s="32">
         <v>700000</v>
@@ -4000,13 +3994,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E10" s="32">
         <v>200000</v>
@@ -4014,13 +4008,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E11" s="32">
         <v>100000</v>
@@ -4028,13 +4022,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E12" s="32">
         <v>100000</v>
@@ -4042,13 +4036,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E13" s="32">
         <v>100000</v>
@@ -4056,13 +4050,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B14" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E14" s="32">
         <v>500000</v>
@@ -4070,10 +4064,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C15" s="35" t="s">
         <v>223</v>
@@ -4084,10 +4078,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>272</v>
@@ -4098,13 +4092,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B17" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E17" s="32">
         <v>500000</v>
@@ -4112,13 +4106,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B18" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E18" s="32">
         <v>700000</v>
@@ -4129,10 +4123,10 @@
         <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C19" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E19" s="32">
         <v>20000</v>
@@ -4143,7 +4137,7 @@
         <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C20" t="s">
         <v>223</v>
@@ -4157,13 +4151,13 @@
         <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C21" s="37" t="s">
         <v>264</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -4171,7 +4165,7 @@
         <v>249</v>
       </c>
       <c r="B22" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>221</v>
@@ -4182,10 +4176,10 @@
         <v>260</v>
       </c>
       <c r="B23" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E23" s="42">
         <v>20000</v>
@@ -11020,7 +11014,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I990"/>
+  <dimension ref="A1:I989"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -11191,7 +11185,7 @@
         <v>0.5</v>
       </c>
       <c r="G7" s="14">
-        <f t="shared" ref="G7:G12" si="1">IF(AND(E7&lt;&gt;0,NOT(ISBLANK(E7)),NOT(ISBLANK(F7))),E7*F7,"")</f>
+        <f t="shared" ref="G7:G11" si="1">IF(AND(E7&lt;&gt;0,NOT(ISBLANK(E7)),NOT(ISBLANK(F7))),E7*F7,"")</f>
         <v>50000</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -11311,34 +11305,7 @@
       </c>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="E12" s="13">
-        <v>100000</v>
-      </c>
-      <c r="F12" s="23">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="I12" s="12"/>
-    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12316,7 +12283,6 @@
     <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -12342,7 +12308,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -12352,7 +12318,7 @@
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -12362,21 +12328,21 @@
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C4" s="23">
         <v>1</v>
@@ -12384,10 +12350,10 @@
     </row>
     <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
@@ -12395,10 +12361,10 @@
     </row>
     <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C6" s="23">
         <v>0.5</v>
@@ -12406,10 +12372,10 @@
     </row>
     <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C7" s="23">
         <v>0.5</v>
@@ -12417,10 +12383,10 @@
     </row>
     <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C8" s="23">
         <v>0.5</v>
@@ -12428,10 +12394,10 @@
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C9" s="23">
         <v>0.4</v>
@@ -12439,10 +12405,10 @@
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C10" s="23">
         <v>0.3</v>
@@ -12450,10 +12416,10 @@
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C11" s="23">
         <v>0.3</v>
@@ -12461,10 +12427,10 @@
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C12" s="23">
         <v>0.3</v>
@@ -12472,10 +12438,10 @@
     </row>
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C13" s="23">
         <v>0.2</v>
@@ -13504,7 +13470,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -13516,7 +13482,7 @@
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="41" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -13530,25 +13496,25 @@
         <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="18" t="s">
         <v>300</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>302</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>116</v>
@@ -13556,7 +13522,7 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B5" s="13">
         <f>COUNTIF(Sales_Stage_Details!A:A,"Lead")</f>
@@ -13570,7 +13536,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F5" s="13">
         <v>7</v>
@@ -13580,10 +13546,10 @@
       </c>
       <c r="H5" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13613,12 +13579,12 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(Sales_Stage_Details!A:A,"Submitted")</f>
@@ -13632,7 +13598,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F7" s="13">
         <v>2</v>
@@ -13645,12 +13611,12 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B8" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Won")</f>
@@ -13676,7 +13642,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13695,7 +13661,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13703,13 +13669,13 @@
         <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>206</v>
@@ -13722,12 +13688,12 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B11" s="14">
         <v>8</v>
@@ -13740,7 +13706,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G11" s="26">
         <v>0.8</v>
@@ -13750,12 +13716,12 @@
         <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
@@ -13770,7 +13736,7 @@
         <v>0.5</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G12" s="26">
         <v>0.85</v>
@@ -13780,12 +13746,12 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B13" s="14">
         <f t="shared" si="0"/>
@@ -13797,7 +13763,7 @@
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G13" s="26">
         <v>0.95</v>
@@ -13807,12 +13773,12 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B14" s="14">
         <f t="shared" si="0"/>
@@ -13827,7 +13793,7 @@
         <v>0.25</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G14" s="26">
         <v>1</v>
@@ -13837,29 +13803,29 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="41" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B16" s="39"/>
       <c r="G16" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>218</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13867,7 +13833,7 @@
         <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -13924,12 +13890,12 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B53D4E-CFA7-4A7F-920E-0B67A45C7121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97C6A1D-D3B5-423E-A8F5-C84806C83F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="340">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -1060,6 +1060,9 @@
   </si>
   <si>
     <t>SAR 100,000</t>
+  </si>
+  <si>
+    <t>Mentorship Program Collections</t>
   </si>
 </sst>
 </file>
@@ -1375,6 +1378,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1384,11 +1392,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1703,24 +1706,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1753,12 +1756,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -4178,10 +4181,10 @@
       <c r="B23" t="s">
         <v>327</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="38">
         <v>20000</v>
       </c>
     </row>
@@ -4204,14 +4207,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5631,32 +5634,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -5678,7 +5681,7 @@
       </c>
       <c r="B5" s="11">
         <f>F11</f>
-        <v>3047376.25</v>
+        <v>3241562.5</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>118</v>
@@ -5693,7 +5696,7 @@
       </c>
       <c r="B6" s="11">
         <f>F13</f>
-        <v>1218950.5</v>
+        <v>1296625</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>118</v>
@@ -5708,7 +5711,7 @@
       </c>
       <c r="B7" s="11">
         <f>F16</f>
-        <v>-1951189.5</v>
+        <v>-1862503</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>118</v>
@@ -5723,7 +5726,7 @@
       </c>
       <c r="B8" s="11">
         <f>F15</f>
-        <v>-3170140</v>
+        <v>-3159128</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>118</v>
@@ -5733,14 +5736,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -5770,17 +5773,17 @@
         <v>0</v>
       </c>
       <c r="C11" s="13">
-        <v>560000</v>
+        <v>570000</v>
       </c>
       <c r="D11" s="13">
-        <v>1043593.75</v>
+        <v>1385625</v>
       </c>
       <c r="E11" s="13">
-        <v>1443782.5</v>
+        <v>1285937.5</v>
       </c>
       <c r="F11" s="14">
         <f>SUM(B11:E11)</f>
-        <v>3047376.25</v>
+        <v>3241562.5</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -5789,17 +5792,17 @@
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13">
-        <v>-336000</v>
+        <v>-342000</v>
       </c>
       <c r="D12" s="13">
-        <v>-626156.25</v>
+        <v>-831375</v>
       </c>
       <c r="E12" s="13">
-        <v>-866269.5</v>
+        <v>-771562.5</v>
       </c>
       <c r="F12" s="14">
         <f>SUM(B12:E12)</f>
-        <v>-1828425.75</v>
+        <v>-1944937.5</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -5812,19 +5815,19 @@
       </c>
       <c r="C13" s="14">
         <f>C11+C12</f>
-        <v>224000</v>
+        <v>228000</v>
       </c>
       <c r="D13" s="14">
         <f>D11+D12</f>
-        <v>417437.5</v>
+        <v>554250</v>
       </c>
       <c r="E13" s="14">
         <f>E11+E12</f>
-        <v>577513</v>
+        <v>514375</v>
       </c>
       <c r="F13" s="14">
         <f>SUM(B13:E13)</f>
-        <v>1218950.5</v>
+        <v>1296625</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -5857,20 +5860,20 @@
         <v>137</v>
       </c>
       <c r="B15" s="13">
-        <v>-775035</v>
+        <v>-786782</v>
       </c>
       <c r="C15" s="13">
-        <v>-825035</v>
+        <v>-786782</v>
       </c>
       <c r="D15" s="13">
-        <v>-775035</v>
+        <v>-786782</v>
       </c>
       <c r="E15" s="13">
-        <v>-795035</v>
+        <v>-798782</v>
       </c>
       <c r="F15" s="14">
         <f>SUM(B15:E15)</f>
-        <v>-3170140</v>
+        <v>-3159128</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
@@ -5879,23 +5882,23 @@
       </c>
       <c r="B16" s="14">
         <f>B13+B15</f>
-        <v>-775035</v>
+        <v>-786782</v>
       </c>
       <c r="C16" s="14">
         <f>C13+C15</f>
-        <v>-601035</v>
+        <v>-558782</v>
       </c>
       <c r="D16" s="14">
         <f>D13+D15</f>
-        <v>-357597.5</v>
+        <v>-232532</v>
       </c>
       <c r="E16" s="14">
         <f>E13+E15</f>
-        <v>-217522</v>
+        <v>-284407</v>
       </c>
       <c r="F16" s="14">
         <f>F13+F15</f>
-        <v>-1951189.5</v>
+        <v>-1862503</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6892,44 +6895,44 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:L1001"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-    </row>
-    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+    </row>
+    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-    </row>
-    <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+    </row>
+    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-    </row>
-    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+    </row>
+    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>113</v>
       </c>
@@ -6943,13 +6946,13 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B5" s="11">
         <f>B11</f>
-        <v>581455</v>
+        <v>581455.34000000008</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>118</v>
@@ -6958,13 +6961,13 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>142</v>
       </c>
       <c r="B6" s="11">
-        <f>F14</f>
-        <v>2213343.75</v>
+        <f>F15</f>
+        <v>2668937.5</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>118</v>
@@ -6973,13 +6976,13 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>144</v>
       </c>
       <c r="B7" s="11">
-        <f>F15+F16</f>
-        <v>-4891206.4399999995</v>
+        <f>F16+F17</f>
+        <v>-5104065.5</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>118</v>
@@ -6988,13 +6991,13 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>146</v>
       </c>
       <c r="B8" s="11">
-        <f>F18</f>
-        <v>-2096407.69</v>
+        <f>F19</f>
+        <v>-1853672.66</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>118</v>
@@ -7003,17 +7006,17 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-    </row>
-    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>127</v>
       </c>
@@ -7033,31 +7036,28 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B11" s="13">
-        <v>581455</v>
+        <v>581455.34000000008</v>
       </c>
       <c r="C11" s="17">
-        <f>B18</f>
-        <v>-86220.689999999944</v>
+        <v>-205326.65999999992</v>
       </c>
       <c r="D11" s="17">
-        <f>C18</f>
-        <v>-969255.69</v>
+        <v>-1056108.6599999999</v>
       </c>
       <c r="E11" s="17">
-        <f>D18</f>
-        <v>-1652946.94</v>
+        <v>-1859265.66</v>
       </c>
       <c r="F11" s="14">
         <f>B11</f>
-        <v>581455</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+        <v>581455.34000000008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>149</v>
       </c>
@@ -7065,20 +7065,20 @@
         <v>0</v>
       </c>
       <c r="C12" s="13">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="D12" s="13">
-        <v>421125</v>
+        <v>500000</v>
       </c>
       <c r="E12" s="13">
-        <v>778182.87</v>
+        <v>900000</v>
       </c>
       <c r="F12" s="13">
-        <f t="shared" ref="F12:F17" si="0">SUM(B12:E12)</f>
-        <v>1229307.8700000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" ref="F12:F18" si="0">SUM(B12:E12)</f>
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>150</v>
       </c>
@@ -7086,169 +7086,188 @@
         <v>0</v>
       </c>
       <c r="C13" s="13">
-        <v>248000</v>
+        <v>278000</v>
       </c>
       <c r="D13" s="13">
-        <v>296375</v>
+        <v>315000</v>
       </c>
       <c r="E13" s="13">
-        <v>439660.88</v>
+        <v>540000</v>
       </c>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
-        <v>984035.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+        <v>1133000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <v>135937.5</v>
+      </c>
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B14" s="14">
-        <f>B12+B13</f>
+      <c r="B15" s="14">
+        <f>B12+B13+B14</f>
         <v>0</v>
       </c>
-      <c r="C14" s="14">
-        <f>C12+C13</f>
+      <c r="C15" s="14">
+        <f>C12+C13+C14</f>
         <v>278000</v>
       </c>
-      <c r="D14" s="14">
-        <f>D12+D13</f>
-        <v>717500</v>
-      </c>
-      <c r="E14" s="14">
-        <f>E12+E13</f>
-        <v>1217843.75</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="D15" s="14">
+        <f t="shared" ref="D15:E15" si="1">D12+D13+D14</f>
+        <v>815000</v>
+      </c>
+      <c r="E15" s="14">
+        <f t="shared" si="1"/>
+        <v>1575937.5</v>
+      </c>
+      <c r="F15" s="14">
         <f t="shared" si="0"/>
-        <v>2213343.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+        <v>2668937.5</v>
+      </c>
+      <c r="J15">
+        <v>-786782</v>
+      </c>
+      <c r="K15">
+        <v>-786782</v>
+      </c>
+      <c r="L15">
+        <v>-798782</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="17">
-        <f>Financial_Overview!B12</f>
+      <c r="B16" s="17">
         <v>0</v>
       </c>
-      <c r="C15" s="17">
-        <f>Financial_Overview!C12</f>
-        <v>-336000</v>
-      </c>
-      <c r="D15" s="17">
-        <f>Financial_Overview!D12</f>
-        <v>-626156.25</v>
-      </c>
-      <c r="E15" s="17">
-        <f>Financial_Overview!E12</f>
-        <v>-866269.5</v>
-      </c>
-      <c r="F15" s="17">
-        <f t="shared" si="0"/>
-        <v>-1828425.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="17">
-        <v>-667675.68999999994</v>
-      </c>
       <c r="C16" s="17">
-        <f>Financial_Overview!C15</f>
-        <v>-825035</v>
+        <v>-342000</v>
       </c>
       <c r="D16" s="17">
-        <f>Financial_Overview!D15</f>
-        <v>-775035</v>
+        <v>-831375</v>
       </c>
       <c r="E16" s="17">
-        <f>Financial_Overview!E15</f>
-        <v>-795035</v>
+        <v>-771562.5</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
-        <v>-3062780.69</v>
+        <v>-1944937.5</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="14">
-        <f>B14+B15+B16</f>
-        <v>-667675.68999999994</v>
-      </c>
-      <c r="C17" s="14">
-        <f>C14+C15+C16</f>
-        <v>-883035</v>
-      </c>
-      <c r="D17" s="14">
-        <f>D14+D15+D16</f>
-        <v>-683691.25</v>
-      </c>
-      <c r="E17" s="14">
-        <f>E14+E15+E16</f>
-        <v>-443460.75</v>
-      </c>
-      <c r="F17" s="14">
+        <v>151</v>
+      </c>
+      <c r="B17" s="17">
+        <v>-786782</v>
+      </c>
+      <c r="C17" s="17">
+        <v>-786782</v>
+      </c>
+      <c r="D17" s="17">
+        <v>-786782</v>
+      </c>
+      <c r="E17" s="17">
+        <v>-798782</v>
+      </c>
+      <c r="F17" s="17">
         <f t="shared" si="0"/>
-        <v>-2677862.69</v>
+        <v>-3159128</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B18" s="14">
-        <f>B11+B17</f>
-        <v>-86220.689999999944</v>
+        <f>B15+B16+B17</f>
+        <v>-786782</v>
       </c>
       <c r="C18" s="14">
-        <f>C11+C17</f>
-        <v>-969255.69</v>
+        <f>C15+C16+C17</f>
+        <v>-850782</v>
       </c>
       <c r="D18" s="14">
-        <f>D11+D17</f>
-        <v>-1652946.94</v>
+        <f>D15+D16+D17</f>
+        <v>-803157</v>
       </c>
       <c r="E18" s="14">
-        <f>E11+E17</f>
-        <v>-2096407.69</v>
+        <f>E15+E16+E17</f>
+        <v>5593</v>
       </c>
       <c r="F18" s="14">
-        <f>E18</f>
-        <v>-2096407.69</v>
+        <f t="shared" si="0"/>
+        <v>-2435128</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="14">
+        <f>B11+B18</f>
+        <v>-205326.65999999992</v>
+      </c>
+      <c r="C19" s="14">
+        <f>C11+C18</f>
+        <v>-1056108.6599999999</v>
+      </c>
+      <c r="D19" s="14">
+        <f>D11+D18</f>
+        <v>-1859265.66</v>
+      </c>
+      <c r="E19" s="14">
+        <f>E11+E18</f>
+        <v>-1853672.66</v>
+      </c>
+      <c r="F19" s="14">
+        <f>E19</f>
+        <v>-1853672.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="14">
-        <f>IF(B18&lt;0,B18,0)</f>
-        <v>-86220.689999999944</v>
-      </c>
-      <c r="C19" s="14">
-        <f>IF(C18&lt;0,C18,0)</f>
-        <v>-969255.69</v>
-      </c>
-      <c r="D19" s="14">
-        <f>IF(D18&lt;0,D18,0)</f>
-        <v>-1652946.94</v>
-      </c>
-      <c r="E19" s="14">
-        <f>IF(E18&lt;0,E18,0)</f>
-        <v>-2096407.69</v>
-      </c>
-      <c r="F19" s="14">
-        <f>MIN(F18,0)</f>
-        <v>-2096407.69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="B20" s="14">
+        <f>IF(B19&lt;0,B19,0)</f>
+        <v>-205326.65999999992</v>
+      </c>
+      <c r="C20" s="14">
+        <f>IF(C19&lt;0,C19,0)</f>
+        <v>-1056108.6599999999</v>
+      </c>
+      <c r="D20" s="14">
+        <f>IF(D19&lt;0,D19,0)</f>
+        <v>-1859265.66</v>
+      </c>
+      <c r="E20" s="14">
+        <f>IF(E19&lt;0,E19,0)</f>
+        <v>-1853672.66</v>
+      </c>
+      <c r="F20" s="14">
+        <f>MIN(F19,0)</f>
+        <v>-1853672.66</v>
+      </c>
+    </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8228,6 +8247,7 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
@@ -8255,32 +8275,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="39"/>
+      <c r="B3" s="42"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -8299,10 +8319,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="39"/>
+      <c r="B7" s="42"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -8368,11 +8388,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -8408,10 +8428,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="39"/>
+      <c r="B17" s="42"/>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8463,10 +8483,10 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="39"/>
+      <c r="B25" s="42"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9508,35 +9528,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -9584,13 +9604,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -9924,14 +9944,14 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="44" t="s">
         <v>243</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9963,19 +9983,19 @@
       </c>
       <c r="C27" s="17">
         <f>Cash_Flow!C12</f>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="D27" s="17">
         <f>Cash_Flow!D12</f>
-        <v>421125</v>
+        <v>500000</v>
       </c>
       <c r="E27" s="17">
         <f>Cash_Flow!E12</f>
-        <v>778182.87</v>
+        <v>900000</v>
       </c>
       <c r="F27" s="17">
         <f>SUM(B27:E27)</f>
-        <v>1229307.8700000001</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9988,19 +10008,19 @@
       </c>
       <c r="C28" s="17">
         <f>Cash_Flow!C13</f>
-        <v>248000</v>
+        <v>278000</v>
       </c>
       <c r="D28" s="17">
         <f>Cash_Flow!D13</f>
-        <v>296375</v>
+        <v>315000</v>
       </c>
       <c r="E28" s="17">
         <f>Cash_Flow!E13</f>
-        <v>439660.88</v>
+        <v>540000</v>
       </c>
       <c r="F28" s="17">
         <f>SUM(B28:E28)</f>
-        <v>984035.88</v>
+        <v>1133000</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10017,15 +10037,15 @@
       </c>
       <c r="D29" s="14">
         <f>D27+D28</f>
-        <v>717500</v>
+        <v>815000</v>
       </c>
       <c r="E29" s="14">
         <f>E27+E28</f>
-        <v>1217843.75</v>
+        <v>1440000</v>
       </c>
       <c r="F29" s="14">
         <f>SUM(B29:E29)</f>
-        <v>2213343.75</v>
+        <v>2533000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11029,28 +11049,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -12307,24 +12327,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -13457,39 +13477,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -13535,7 +13555,7 @@
       <c r="D5" s="13">
         <v>2</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>302</v>
       </c>
       <c r="F5" s="13">
@@ -13646,13 +13666,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
       <c r="G9" s="26">
         <v>0.6</v>
       </c>
@@ -13807,17 +13827,17 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="B16" s="39"/>
+      <c r="B16" s="42"/>
       <c r="G16" s="18" t="s">
         <v>315</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,25 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Dar Al Riyadh\Safaa\Updates\27.04.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97C6A1D-D3B5-423E-A8F5-C84806C83F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C773022E-2213-4C36-87B3-A3A729952EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Dashboard_Map" sheetId="2" r:id="rId2"/>
     <sheet name="Financial_Overview" sheetId="3" r:id="rId3"/>
     <sheet name="Cash_Flow" sheetId="4" r:id="rId4"/>
-    <sheet name="Strategy_Operations" sheetId="5" r:id="rId5"/>
-    <sheet name="Pipeline_Revenue" sheetId="6" r:id="rId6"/>
+    <sheet name="Pipeline_Revenue" sheetId="6" r:id="rId5"/>
+    <sheet name="Strategy_Operations" sheetId="5" r:id="rId6"/>
     <sheet name="Sales_Raw_Opportunities" sheetId="7" r:id="rId7"/>
-    <sheet name="Sales_Raw_Operations" sheetId="8" r:id="rId8"/>
-    <sheet name="Sales_Performance" sheetId="9" r:id="rId9"/>
-    <sheet name="Lists" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet name="Sales_Stage_Details" sheetId="11" r:id="rId11"/>
+    <sheet name="Sales_Performance" sheetId="9" r:id="rId8"/>
+    <sheet name="Sales_Stage_Details" sheetId="11" r:id="rId9"/>
+    <sheet name="Sales_Raw_Operations" sheetId="8" r:id="rId10"/>
+    <sheet name="Lists" sheetId="10" state="hidden" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="363">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -810,42 +810,15 @@
     <t>ESG Certificate</t>
   </si>
   <si>
-    <t>Salwa AlSudairy</t>
-  </si>
-  <si>
-    <t>Jan 2026</t>
-  </si>
-  <si>
-    <t>KSA Sustainability Champions</t>
-  </si>
-  <si>
-    <t>Dec 2025</t>
-  </si>
-  <si>
     <t>Tadawul Group</t>
   </si>
   <si>
     <t>Won</t>
   </si>
   <si>
-    <t>GOSI</t>
-  </si>
-  <si>
-    <t>Enablement Program</t>
-  </si>
-  <si>
-    <t>Feb 2026</t>
-  </si>
-  <si>
     <t>Middle Beast</t>
   </si>
   <si>
-    <t>Attache ESG Enablement</t>
-  </si>
-  <si>
-    <t>Mar 2026</t>
-  </si>
-  <si>
     <t>ESG Integration</t>
   </si>
   <si>
@@ -858,15 +831,9 @@
     <t>CMA</t>
   </si>
   <si>
-    <t>Green Finance Think Tank</t>
-  </si>
-  <si>
     <t>ITQAN</t>
   </si>
   <si>
-    <t>Tadawul ESG Course</t>
-  </si>
-  <si>
     <t>Lost</t>
   </si>
   <si>
@@ -954,9 +921,6 @@
     <t>1000000</t>
   </si>
   <si>
-    <t>Auto-count from raw opportunities</t>
-  </si>
-  <si>
     <t>Proposals Submitted</t>
   </si>
   <si>
@@ -1029,9 +993,6 @@
     <t>This Week</t>
   </si>
   <si>
-    <t xml:space="preserve">Nadec </t>
-  </si>
-  <si>
     <t>Riyadh Air</t>
   </si>
   <si>
@@ -1041,59 +1002,152 @@
     <t>Nestle</t>
   </si>
   <si>
-    <t>Kpmg</t>
-  </si>
-  <si>
     <t>EY</t>
   </si>
   <si>
-    <t>Accenture</t>
-  </si>
-  <si>
     <t>NCFB</t>
   </si>
   <si>
     <t>Humain</t>
   </si>
   <si>
-    <t>CFG</t>
-  </si>
-  <si>
     <t>SAR 100,000</t>
   </si>
   <si>
     <t>Mentorship Program Collections</t>
+  </si>
+  <si>
+    <t>ESG and Corporate Governance Enablement</t>
+  </si>
+  <si>
+    <t>ESG Workshop</t>
+  </si>
+  <si>
+    <t>Acceselerating Success for the KSA Sustainability Champions Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attache ESG Enablement </t>
+  </si>
+  <si>
+    <t>Obeikan</t>
+  </si>
+  <si>
+    <t>RPI ESG Workshop</t>
+  </si>
+  <si>
+    <t>PIF</t>
+  </si>
+  <si>
+    <t>PIF Offsite Proposal</t>
+  </si>
+  <si>
+    <t>Center For Government</t>
+  </si>
+  <si>
+    <t>ESG and Sustainability Course Development</t>
+  </si>
+  <si>
+    <t>Monshaat ESG Course</t>
+  </si>
+  <si>
+    <t>SIDF</t>
+  </si>
+  <si>
+    <t>ESG and Corporate Governance Graduate Enablement</t>
+  </si>
+  <si>
+    <t>GDP ESG Workshop</t>
+  </si>
+  <si>
+    <t>Sustainable Finance /MEP Campaign</t>
+  </si>
+  <si>
+    <t>AI &amp; Governance</t>
+  </si>
+  <si>
+    <t>Community Education</t>
+  </si>
+  <si>
+    <t>Anti Money laundry /Fraud Cousre</t>
+  </si>
+  <si>
+    <t>ESG Academy</t>
+  </si>
+  <si>
+    <t>KPMG</t>
+  </si>
+  <si>
+    <t>Environmental Training</t>
+  </si>
+  <si>
+    <t>Mentorship Program</t>
+  </si>
+  <si>
+    <t>Gosi-Mentorship</t>
+  </si>
+  <si>
+    <t>Mentorship Platfrom</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Alinma Bank</t>
+  </si>
+  <si>
+    <t>SABIC</t>
+  </si>
+  <si>
+    <t>Amaal Fathani</t>
+  </si>
+  <si>
+    <t>Yat Governance Center</t>
+  </si>
+  <si>
+    <t>Kaplan</t>
+  </si>
+  <si>
+    <t>National Company for Mechanichal Systems(NCMS)</t>
+  </si>
+  <si>
+    <t>CMA(Fantec)</t>
+  </si>
+  <si>
+    <t>Governance Training &amp; Social Imapct Measurment</t>
+  </si>
+  <si>
+    <t>MEP Sustanability Champion Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University Partnership </t>
+  </si>
+  <si>
+    <t>Anti Money Laundering Courses Partnership</t>
+  </si>
+  <si>
+    <t>ESG Training Certification Partnership</t>
+  </si>
+  <si>
+    <t>Coperate Governance Model</t>
+  </si>
+  <si>
+    <t>Supporting Fentec Saudi on Sustainable Investment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1188,14 +1242,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1228,7 +1274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1252,146 +1298,124 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1472,7 +1496,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I34">
+  <autoFilter ref="A3:I34" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="3">
+      <filters>
+        <dateGroupItem year="2026" month="4" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Client"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Opportunity"/>
@@ -1480,7 +1511,9 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Submitted"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Value_SAR"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Probability_Pct"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Weighted_Value_SAR"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Weighted_Value_SAR">
+      <calculatedColumnFormula>IF(AND(E4&lt;&gt;0,NOT(ISBLANK(E4)),NOT(ISBLANK(F4))),E4*F4,"")</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Stage"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Notes"/>
   </tableColumns>
@@ -1706,24 +1739,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1756,12 +1789,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -2846,6 +2879,1150 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+    </row>
+    <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" s="23">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="23">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2855,18 +4032,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -2874,22 +4051,22 @@
         <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3878,321 +5055,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="52" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" t="s">
-        <v>327</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="E5" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="E6" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>320</v>
-      </c>
-      <c r="B7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="E7" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" t="s">
-        <v>327</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>329</v>
-      </c>
-      <c r="E8" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>320</v>
-      </c>
-      <c r="B9" t="s">
-        <v>327</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="E9" s="32">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B10" t="s">
-        <v>327</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>331</v>
-      </c>
-      <c r="E10" s="32">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B11" t="s">
-        <v>327</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>332</v>
-      </c>
-      <c r="E11" s="32">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>320</v>
-      </c>
-      <c r="B12" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E12" s="32">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B13" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>334</v>
-      </c>
-      <c r="E13" s="32">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B14" t="s">
-        <v>327</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>335</v>
-      </c>
-      <c r="E14" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>321</v>
-      </c>
-      <c r="B15" t="s">
-        <v>327</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="E15" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>321</v>
-      </c>
-      <c r="B16" t="s">
-        <v>327</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="E16" s="32">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>321</v>
-      </c>
-      <c r="B17" t="s">
-        <v>327</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="E17" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" t="s">
-        <v>327</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="E18" s="32">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>249</v>
-      </c>
-      <c r="B19" t="s">
-        <v>327</v>
-      </c>
-      <c r="C19" t="s">
-        <v>337</v>
-      </c>
-      <c r="E19" s="32">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>249</v>
-      </c>
-      <c r="B20" t="s">
-        <v>327</v>
-      </c>
-      <c r="C20" t="s">
-        <v>223</v>
-      </c>
-      <c r="E20" s="32">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" t="s">
-        <v>327</v>
-      </c>
-      <c r="C21" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>249</v>
-      </c>
-      <c r="B22" t="s">
-        <v>327</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>260</v>
-      </c>
-      <c r="B23" t="s">
-        <v>327</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="E23" s="38">
-        <v>20000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F1000"/>
@@ -4207,14 +5069,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5634,32 +6496,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -5736,14 +6598,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -6905,32 +7767,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -7007,14 +7869,14 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -7101,7 +7963,7 @@
     </row>
     <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="B14" s="13">
         <v>0</v>
@@ -8261,6 +9123,1525 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="26" width="8.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+    </row>
+    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="14">
+        <f>SUM(D11:D22)</f>
+        <v>3047378</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2100000</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="21">
+        <v>4</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <f t="shared" ref="D11:D22" si="0">B11+C11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H11" s="22">
+        <v>500000</v>
+      </c>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H12" s="22">
+        <v>500000</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13">
+        <v>30000</v>
+      </c>
+      <c r="D13" s="14">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="22">
+        <v>350000</v>
+      </c>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>90000</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="0"/>
+        <v>90000</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" s="22">
+        <v>330000</v>
+      </c>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="13">
+        <v>100000</v>
+      </c>
+      <c r="C15" s="13">
+        <v>40000</v>
+      </c>
+      <c r="D15" s="14">
+        <f t="shared" si="0"/>
+        <v>140000</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H15" s="22">
+        <v>220000</v>
+      </c>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="13">
+        <v>185000</v>
+      </c>
+      <c r="C16" s="13">
+        <v>115000</v>
+      </c>
+      <c r="D16" s="14">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H16" s="22">
+        <v>70000</v>
+      </c>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="13">
+        <v>136125</v>
+      </c>
+      <c r="C17" s="13">
+        <v>111375</v>
+      </c>
+      <c r="D17" s="14">
+        <f t="shared" si="0"/>
+        <v>247500</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H17" s="22">
+        <v>50000</v>
+      </c>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="13">
+        <v>170156</v>
+      </c>
+      <c r="C18" s="13">
+        <v>139219</v>
+      </c>
+      <c r="D18" s="14">
+        <f t="shared" si="0"/>
+        <v>309375</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H18" s="22">
+        <v>45000</v>
+      </c>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B19" s="13">
+        <v>331064</v>
+      </c>
+      <c r="C19" s="13">
+        <v>155655</v>
+      </c>
+      <c r="D19" s="14">
+        <f t="shared" si="0"/>
+        <v>486719</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H19" s="22">
+        <v>30000</v>
+      </c>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="13">
+        <v>276963</v>
+      </c>
+      <c r="C20" s="13">
+        <v>144788</v>
+      </c>
+      <c r="D20" s="14">
+        <f t="shared" si="0"/>
+        <v>421751</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H20" s="21">
+        <f>SUM(H11:H19)</f>
+        <v>2095000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B21" s="13">
+        <v>330051</v>
+      </c>
+      <c r="C21" s="13">
+        <v>188224</v>
+      </c>
+      <c r="D21" s="14">
+        <f t="shared" si="0"/>
+        <v>518275</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" s="13">
+        <v>299067</v>
+      </c>
+      <c r="C22" s="13">
+        <v>204691</v>
+      </c>
+      <c r="D22" s="14">
+        <f t="shared" si="0"/>
+        <v>503758</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B23" s="14">
+        <f>SUM(B11:B22)</f>
+        <v>1828426</v>
+      </c>
+      <c r="C23" s="14">
+        <f>SUM(C11:C22)</f>
+        <v>1218952</v>
+      </c>
+      <c r="D23" s="14">
+        <f>SUM(D11:D22)</f>
+        <v>3047378</v>
+      </c>
+      <c r="E23" s="12"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="17">
+        <f>Cash_Flow!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="17">
+        <f>Cash_Flow!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="17">
+        <f>Cash_Flow!D12</f>
+        <v>500000</v>
+      </c>
+      <c r="E27" s="17">
+        <f>Cash_Flow!E12</f>
+        <v>900000</v>
+      </c>
+      <c r="F27" s="17">
+        <f>SUM(B27:E27)</f>
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" s="17">
+        <f>Cash_Flow!B13</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="17">
+        <f>Cash_Flow!C13</f>
+        <v>278000</v>
+      </c>
+      <c r="D28" s="17">
+        <f>Cash_Flow!D13</f>
+        <v>315000</v>
+      </c>
+      <c r="E28" s="17">
+        <f>Cash_Flow!E13</f>
+        <v>540000</v>
+      </c>
+      <c r="F28" s="17">
+        <f>SUM(B28:E28)</f>
+        <v>1133000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B29" s="14">
+        <f>B27+B28</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="14">
+        <f>C27+C28</f>
+        <v>278000</v>
+      </c>
+      <c r="D29" s="14">
+        <f>D27+D28</f>
+        <v>815000</v>
+      </c>
+      <c r="E29" s="14">
+        <f>E27+E28</f>
+        <v>1440000</v>
+      </c>
+      <c r="F29" s="14">
+        <f>SUM(B29:E29)</f>
+        <v>2533000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8275,32 +10656,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="42"/>
+      <c r="B3" s="33"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -8319,10 +10700,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="42"/>
+      <c r="B7" s="33"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -8388,11 +10769,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -8428,10 +10809,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="42"/>
+      <c r="B17" s="33"/>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8483,10 +10864,10 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="42"/>
+      <c r="B25" s="33"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9513,1525 +11894,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="26" width="8.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-    </row>
-    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" s="14">
-        <f>SUM(D11:D22)</f>
-        <v>3047378</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B6" s="13">
-        <v>2100000</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="21">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-    </row>
-    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="13">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13">
-        <v>0</v>
-      </c>
-      <c r="D11" s="14">
-        <f t="shared" ref="D11:D22" si="0">B11+C11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H11" s="22">
-        <v>500000</v>
-      </c>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B12" s="13">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="H12" s="22">
-        <v>500000</v>
-      </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" s="13">
-        <v>0</v>
-      </c>
-      <c r="C13" s="13">
-        <v>30000</v>
-      </c>
-      <c r="D13" s="14">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H13" s="22">
-        <v>350000</v>
-      </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B14" s="13">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13">
-        <v>90000</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="0"/>
-        <v>90000</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H14" s="22">
-        <v>330000</v>
-      </c>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="13">
-        <v>100000</v>
-      </c>
-      <c r="C15" s="13">
-        <v>40000</v>
-      </c>
-      <c r="D15" s="14">
-        <f t="shared" si="0"/>
-        <v>140000</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H15" s="22">
-        <v>220000</v>
-      </c>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B16" s="13">
-        <v>185000</v>
-      </c>
-      <c r="C16" s="13">
-        <v>115000</v>
-      </c>
-      <c r="D16" s="14">
-        <f t="shared" si="0"/>
-        <v>300000</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H16" s="22">
-        <v>70000</v>
-      </c>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B17" s="13">
-        <v>136125</v>
-      </c>
-      <c r="C17" s="13">
-        <v>111375</v>
-      </c>
-      <c r="D17" s="14">
-        <f t="shared" si="0"/>
-        <v>247500</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H17" s="22">
-        <v>50000</v>
-      </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B18" s="13">
-        <v>170156</v>
-      </c>
-      <c r="C18" s="13">
-        <v>139219</v>
-      </c>
-      <c r="D18" s="14">
-        <f t="shared" si="0"/>
-        <v>309375</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="H18" s="22">
-        <v>45000</v>
-      </c>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B19" s="13">
-        <v>331064</v>
-      </c>
-      <c r="C19" s="13">
-        <v>155655</v>
-      </c>
-      <c r="D19" s="14">
-        <f t="shared" si="0"/>
-        <v>486719</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="H19" s="22">
-        <v>30000</v>
-      </c>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="13">
-        <v>276963</v>
-      </c>
-      <c r="C20" s="13">
-        <v>144788</v>
-      </c>
-      <c r="D20" s="14">
-        <f t="shared" si="0"/>
-        <v>421751</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="H20" s="21">
-        <f>SUM(H11:H19)</f>
-        <v>2095000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B21" s="13">
-        <v>330051</v>
-      </c>
-      <c r="C21" s="13">
-        <v>188224</v>
-      </c>
-      <c r="D21" s="14">
-        <f t="shared" si="0"/>
-        <v>518275</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B22" s="13">
-        <v>299067</v>
-      </c>
-      <c r="C22" s="13">
-        <v>204691</v>
-      </c>
-      <c r="D22" s="14">
-        <f t="shared" si="0"/>
-        <v>503758</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B23" s="14">
-        <f>SUM(B11:B22)</f>
-        <v>1828426</v>
-      </c>
-      <c r="C23" s="14">
-        <f>SUM(C11:C22)</f>
-        <v>1218952</v>
-      </c>
-      <c r="D23" s="14">
-        <f>SUM(D11:D22)</f>
-        <v>3047378</v>
-      </c>
-      <c r="E23" s="12"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="44" t="s">
-        <v>243</v>
-      </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B27" s="17">
-        <f>Cash_Flow!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="17">
-        <f>Cash_Flow!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="17">
-        <f>Cash_Flow!D12</f>
-        <v>500000</v>
-      </c>
-      <c r="E27" s="17">
-        <f>Cash_Flow!E12</f>
-        <v>900000</v>
-      </c>
-      <c r="F27" s="17">
-        <f>SUM(B27:E27)</f>
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B28" s="17">
-        <f>Cash_Flow!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="17">
-        <f>Cash_Flow!C13</f>
-        <v>278000</v>
-      </c>
-      <c r="D28" s="17">
-        <f>Cash_Flow!D13</f>
-        <v>315000</v>
-      </c>
-      <c r="E28" s="17">
-        <f>Cash_Flow!E13</f>
-        <v>540000</v>
-      </c>
-      <c r="F28" s="17">
-        <f>SUM(B28:E28)</f>
-        <v>1133000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B29" s="14">
-        <f>B27+B28</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="14">
-        <f>C27+C28</f>
-        <v>278000</v>
-      </c>
-      <c r="D29" s="14">
-        <f>D27+D28</f>
-        <v>815000</v>
-      </c>
-      <c r="E29" s="14">
-        <f>E27+E28</f>
-        <v>1440000</v>
-      </c>
-      <c r="F29" s="14">
-        <f>SUM(B29:E29)</f>
-        <v>2533000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A25:F25"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I989"/>
@@ -11049,28 +11911,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -11101,267 +11963,783 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
+      </c>
+      <c r="D4" s="42">
+        <v>45935</v>
       </c>
       <c r="E4" s="13">
-        <v>30000</v>
+        <v>400000</v>
       </c>
       <c r="F4" s="23">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="14">
-        <f t="shared" ref="G4:G6" si="0">IF(AND(E4&lt;&gt;0,NOT(ISBLANK(E4)),NOT(ISBLANK(F4))),E4*F4,"")</f>
-        <v>28500</v>
+        <f>IF(AND(E4&lt;&gt;0,NOT(ISBLANK(E4)),NOT(ISBLANK(F4))),E4*F4,"")</f>
+        <v>120000</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>223</v>
+        <v>332</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>257</v>
+        <v>334</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
+      </c>
+      <c r="D5" s="42">
+        <v>46120</v>
       </c>
       <c r="E5" s="13">
-        <v>500000</v>
+        <v>20000</v>
       </c>
       <c r="F5" s="23">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="14">
-        <f t="shared" si="0"/>
-        <v>425000</v>
+        <f>IF(AND(E5&lt;&gt;0,NOT(ISBLANK(E5)),NOT(ISBLANK(F5))),E5*F5,"")</f>
+        <v>16000</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>262</v>
+        <v>339</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>263</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="13">
         <v>500000</v>
       </c>
       <c r="F6" s="23">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="14">
-        <f t="shared" si="0"/>
-        <v>300000</v>
+        <f>IF(AND(E6&lt;&gt;0,NOT(ISBLANK(E6)),NOT(ISBLANK(F6))),E6*F6,"")</f>
+        <v>200000</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>265</v>
+        <v>340</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>266</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D7" s="12"/>
       <c r="E7" s="13">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="F7" s="23">
         <v>0.5</v>
       </c>
       <c r="G7" s="14">
-        <f t="shared" ref="G7:G11" si="1">IF(AND(E7&lt;&gt;0,NOT(ISBLANK(E7)),NOT(ISBLANK(F7))),E7*F7,"")</f>
-        <v>50000</v>
+        <f>IF(AND(E7&lt;&gt;0,NOT(ISBLANK(E7)),NOT(ISBLANK(F7))),E7*F7,"")</f>
+        <v>350000</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>221</v>
+        <v>316</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>267</v>
+        <v>341</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>263</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D8" s="12"/>
       <c r="E8" s="13">
-        <v>500000</v>
+        <v>60000</v>
       </c>
       <c r="F8" s="23">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G8" s="14">
-        <f t="shared" si="1"/>
-        <v>250000</v>
+        <f>IF(AND(E8&lt;&gt;0,NOT(ISBLANK(E8)),NOT(ISBLANK(F8))),E8*F8,"")</f>
+        <v>36000</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>256</v>
-      </c>
+      <c r="D9" s="12"/>
       <c r="E9" s="13">
-        <v>90000</v>
+        <v>200000</v>
       </c>
       <c r="F9" s="23">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="14">
-        <f t="shared" si="1"/>
-        <v>45000</v>
+        <f>IF(AND(E9&lt;&gt;0,NOT(ISBLANK(E9)),NOT(ISBLANK(F9))),E9*F9,"")</f>
+        <v>60000</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>270</v>
+        <v>343</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>271</v>
+        <v>344</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>266</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D10" s="12"/>
       <c r="E10" s="13">
         <v>100000</v>
       </c>
       <c r="F10" s="23">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G10" s="14">
-        <f t="shared" si="1"/>
-        <v>50000</v>
+        <f>IF(AND(E10&lt;&gt;0,NOT(ISBLANK(E10)),NOT(ISBLANK(F10))),E10*F10,"")</f>
+        <v>30000</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>249</v>
+        <v>348</v>
       </c>
       <c r="I10" s="12"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="42">
+        <v>46131</v>
+      </c>
+      <c r="E11" s="13">
+        <v>256000</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="14">
+        <f>IF(AND(E11&lt;&gt;0,NOT(ISBLANK(E11)),NOT(ISBLANK(F11))),E11*F11,"")</f>
+        <v>204800</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="B12" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" s="43">
+        <v>45894</v>
+      </c>
+      <c r="E12" s="39">
+        <v>45000</v>
+      </c>
+      <c r="F12" s="40">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <f>IF(AND(E12&lt;&gt;0,NOT(ISBLANK(E12)),NOT(ISBLANK(F12))),E12*F12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I12" s="38"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="43">
+        <v>45988</v>
+      </c>
+      <c r="E13" s="39">
+        <v>140000</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <f>IF(AND(E13&lt;&gt;0,NOT(ISBLANK(E13)),NOT(ISBLANK(F13))),E13*F13,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I13" s="38"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" s="43">
+        <v>45991</v>
+      </c>
+      <c r="E14" s="39">
+        <v>70000</v>
+      </c>
+      <c r="F14" s="23">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f>IF(AND(E14&lt;&gt;0,NOT(ISBLANK(E14)),NOT(ISBLANK(F14))),E14*F14,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I14" s="38"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" s="43">
+        <v>46015</v>
+      </c>
+      <c r="E15" s="39">
+        <v>100000</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <f>IF(AND(E15&lt;&gt;0,NOT(ISBLANK(E15)),NOT(ISBLANK(F15))),E15*F15,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I15" s="38"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" s="43">
+        <v>45922</v>
+      </c>
+      <c r="E16" s="39">
+        <v>75000</v>
+      </c>
+      <c r="F16" s="23">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <f>IF(AND(E16&lt;&gt;0,NOT(ISBLANK(E16)),NOT(ISBLANK(F16))),E16*F16,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I16" s="38"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="B17" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" s="43">
+        <v>45890</v>
+      </c>
+      <c r="E17" s="39">
+        <v>0</v>
+      </c>
+      <c r="F17" s="23">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="str">
+        <f>IF(AND(E17&lt;&gt;0,NOT(ISBLANK(E17)),NOT(ISBLANK(F17))),E17*F17,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="E11" s="13">
+      <c r="I17" s="38"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D18" s="43">
+        <v>46047</v>
+      </c>
+      <c r="E18" s="39">
+        <v>90000</v>
+      </c>
+      <c r="F18" s="40">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <f>IF(AND(E18&lt;&gt;0,NOT(ISBLANK(E18)),NOT(ISBLANK(F18))),E18*F18,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I18" s="38"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D19" s="43">
+        <v>45958</v>
+      </c>
+      <c r="E19" s="39">
+        <v>60000</v>
+      </c>
+      <c r="F19" s="40">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <f>IF(AND(E19&lt;&gt;0,NOT(ISBLANK(E19)),NOT(ISBLANK(F19))),E19*F19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I19" s="38"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" s="43">
+        <v>45942</v>
+      </c>
+      <c r="E20" s="39">
+        <v>68000</v>
+      </c>
+      <c r="F20" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="14">
+        <f>IF(AND(E20&lt;&gt;0,NOT(ISBLANK(E20)),NOT(ISBLANK(F20))),E20*F20,"")</f>
+        <v>34000</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>310</v>
+      </c>
+      <c r="I20" s="38"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" s="38"/>
+      <c r="E21" s="39">
+        <v>100000</v>
+      </c>
+      <c r="F21" s="40">
+        <v>0.4</v>
+      </c>
+      <c r="G21" s="14">
+        <f>IF(AND(E21&lt;&gt;0,NOT(ISBLANK(E21)),NOT(ISBLANK(F21))),E21*F21,"")</f>
+        <v>40000</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>310</v>
+      </c>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D22" s="43">
+        <v>46000</v>
+      </c>
+      <c r="E22" s="39">
+        <v>500000</v>
+      </c>
+      <c r="F22" s="40">
+        <v>0.85</v>
+      </c>
+      <c r="G22" s="14">
+        <f>IF(AND(E22&lt;&gt;0,NOT(ISBLANK(E22)),NOT(ISBLANK(F22))),E22*F22,"")</f>
+        <v>425000</v>
+      </c>
+      <c r="H22" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="I22" s="38"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="43">
+        <v>46083</v>
+      </c>
+      <c r="E23" s="39">
+        <v>100000</v>
+      </c>
+      <c r="F23" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="14">
+        <f>IF(AND(E23&lt;&gt;0,NOT(ISBLANK(E23)),NOT(ISBLANK(F23))),E23*F23,"")</f>
+        <v>50000</v>
+      </c>
+      <c r="H23" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="I23" s="38"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24" s="43">
+        <v>46054</v>
+      </c>
+      <c r="E24" s="39">
+        <v>500000</v>
+      </c>
+      <c r="F24" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="14">
+        <f>IF(AND(E24&lt;&gt;0,NOT(ISBLANK(E24)),NOT(ISBLANK(F24))),E24*F24,"")</f>
+        <v>250000</v>
+      </c>
+      <c r="H24" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="I24" s="38"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" s="38"/>
+      <c r="E25" s="39">
+        <v>180000</v>
+      </c>
+      <c r="F25" s="40">
+        <v>0.6</v>
+      </c>
+      <c r="G25" s="14">
+        <f>IF(AND(E25&lt;&gt;0,NOT(ISBLANK(E25)),NOT(ISBLANK(F25))),E25*F25,"")</f>
+        <v>108000</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="I25" s="38"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D26" s="43">
+        <v>46091</v>
+      </c>
+      <c r="E26" s="39">
+        <v>100000</v>
+      </c>
+      <c r="F26" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="14">
+        <f>IF(AND(E26&lt;&gt;0,NOT(ISBLANK(E26)),NOT(ISBLANK(F26))),E26*F26,"")</f>
+        <v>50000</v>
+      </c>
+      <c r="H26" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="I26" s="38"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="D27" s="43">
+        <v>46040</v>
+      </c>
+      <c r="E27" s="39">
         <v>30000</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F27" s="40">
         <v>1</v>
       </c>
-      <c r="G11" s="14">
-        <f t="shared" si="1"/>
+      <c r="G27" s="14">
+        <f>IF(AND(E27&lt;&gt;0,NOT(ISBLANK(E27)),NOT(ISBLANK(F27))),E27*F27,"")</f>
         <v>30000</v>
       </c>
-      <c r="H11" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="H27" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="I27" s="38"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>349</v>
+      </c>
+      <c r="B28" t="s">
+        <v>356</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" ref="G28:G34" si="0">IF(AND(E28&lt;&gt;0,NOT(ISBLANK(E28)),NOT(ISBLANK(F28))),E28*F28,"")</f>
+        <v/>
+      </c>
+      <c r="H28" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>350</v>
+      </c>
+      <c r="B29" t="s">
+        <v>357</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H29" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B30" t="s">
+        <v>358</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H30" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>352</v>
+      </c>
+      <c r="B31" t="s">
+        <v>359</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H31" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>353</v>
+      </c>
+      <c r="B32" t="s">
+        <v>360</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>354</v>
+      </c>
+      <c r="B33" t="s">
+        <v>361</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H33" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>355</v>
+      </c>
+      <c r="B34" t="s">
+        <v>362</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H34" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12317,1150 +13695,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="26" width="8.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
-        <v>275</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-    </row>
-    <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-    </row>
-    <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="C4" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C7" s="23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C8" s="23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C9" s="23">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C10" s="23">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="C11" s="23">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C12" s="23">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="C13" s="23">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -13477,64 +13711,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="A2" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
-        <v>294</v>
-      </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
+      <c r="A3" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>116</v>
@@ -13542,109 +13776,94 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B5" s="13">
-        <f>COUNTIF(Sales_Stage_Details!A:A,"Lead")</f>
-        <v>10</v>
-      </c>
-      <c r="C5" s="13">
-        <f>SUMIF(Sales_Stage_Details!A:A,"Lead",Sales_Stage_Details!E:E)</f>
-        <v>3700000</v>
-      </c>
+        <f>COUNTIFS(Table_1[Stage],"Lead")</f>
+        <v>7</v>
+      </c>
+      <c r="C5" s="13"/>
       <c r="D5" s="13">
         <v>2</v>
       </c>
-      <c r="E5" s="40" t="s">
-        <v>302</v>
-      </c>
-      <c r="F5" s="13">
-        <v>7</v>
-      </c>
+      <c r="E5" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="F5" s="13"/>
       <c r="G5" s="25">
         <v>0</v>
       </c>
       <c r="H5" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G5)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B6" s="13">
-        <f>COUNTIF(Sales_Stage_Details!A:A,"Active Proposal")</f>
-        <v>4</v>
+        <f>COUNTIFS(Table_1[Stage],"Active")</f>
+        <v>8</v>
       </c>
       <c r="C6" s="13">
-        <f>SUMIF(Sales_Stage_Details!A:A,"Active Proposal",Sales_Stage_Details!E:E)</f>
-        <v>2100000</v>
+        <f>SUMIF(Table_1[Stage],"Active",Table_1[Weighted_Value_SAR])</f>
+        <v>1016800</v>
       </c>
       <c r="D6" s="13">
         <v>0</v>
       </c>
       <c r="E6" s="24"/>
-      <c r="F6" s="13">
-        <v>4</v>
-      </c>
+      <c r="F6" s="44"/>
       <c r="G6" s="25">
         <v>0.3</v>
       </c>
       <c r="H6" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G6)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B7" s="13">
-        <f>COUNTIF(Sales_Stage_Details!A:A,"Submitted")</f>
+        <f>COUNTIFS(Table_1[Stage],"Submitted")</f>
         <v>4</v>
       </c>
       <c r="C7" s="13">
-        <f>SUMIF(Sales_Stage_Details!A:A,"Submitted",Sales_Stage_Details!E:E)</f>
-        <v>520000</v>
+        <f>SUMIF(Table_1[Stage],"Submitted",Table_1[Weighted_Value_SAR])</f>
+        <v>833000</v>
       </c>
       <c r="D7" s="13">
         <v>1</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>338</v>
-      </c>
-      <c r="F7" s="13">
-        <v>2</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="F7" s="13"/>
       <c r="G7" s="25">
         <v>0.4</v>
       </c>
       <c r="H7" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G7)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B8" s="13">
-        <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Won")</f>
-        <v>1</v>
+        <f>COUNTIFS(Table_1[Stage],"Won")</f>
+        <v>2</v>
       </c>
       <c r="C8" s="13">
-        <f>SUMIF(Sales_Raw_Opportunities!H:H,"Won",Sales_Raw_Opportunities!E:E)</f>
-        <v>30000</v>
+        <f>SUMIF(Table_1[Stage],"Won",Table_1[Value_SAR])</f>
+        <v>130000</v>
       </c>
       <c r="D8" s="13">
         <f>COUNTIFS(Sales_Raw_Opportunities!H:H,"Won",Sales_Raw_Opportunities!D:D,"Apr 2026")</f>
@@ -13659,43 +13878,39 @@
       </c>
       <c r="H8" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G8)</f>
-        <v>4</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
       <c r="G9" s="26">
         <v>0.6</v>
       </c>
       <c r="H9" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G9)</f>
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>206</v>
@@ -13707,56 +13922,52 @@
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>303</v>
-      </c>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="B11" s="14">
         <v>8</v>
       </c>
       <c r="C11" s="14">
         <f t="shared" ref="B11:C14" si="0">C5</f>
-        <v>3700000</v>
+        <v>0</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="G11" s="26">
         <v>0.8</v>
       </c>
       <c r="H11" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G11)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C12" s="14">
         <f t="shared" si="0"/>
-        <v>2100000</v>
+        <v>1016800</v>
       </c>
       <c r="D12" s="15">
         <f>IFERROR(B12/B11,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="G12" s="26">
         <v>0.85</v>
@@ -13765,13 +13976,11 @@
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G12)</f>
         <v>1</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>303</v>
-      </c>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B13" s="14">
         <f t="shared" si="0"/>
@@ -13779,41 +13988,39 @@
       </c>
       <c r="C13" s="14">
         <f t="shared" si="0"/>
-        <v>520000</v>
+        <v>833000</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="G13" s="26">
         <v>0.95</v>
       </c>
       <c r="H13" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G13)</f>
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B14" s="14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="14">
         <f t="shared" si="0"/>
-        <v>30000</v>
+        <v>130000</v>
       </c>
       <c r="D14" s="15">
         <f>IFERROR(B14/B13,0)</f>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="G14" s="26">
         <v>1</v>
@@ -13822,30 +14029,28 @@
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G14)</f>
         <v>1</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+    </row>
+    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="G16" s="18" t="s">
         <v>303</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="44" t="s">
-        <v>313</v>
-      </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-    </row>
-    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="B16" s="42"/>
-      <c r="G16" s="18" t="s">
-        <v>315</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>218</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -13853,7 +14058,7 @@
         <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -13910,12 +14115,12 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -14904,4 +15109,161 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C5" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E6">
+        <v>256000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>315</v>
+      </c>
+      <c r="C11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Dar Al Riyadh\HTML\Safaa 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\safa update\12.05.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8101C1-CCD2-47EC-8AEE-20B937196BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A7B63F-87D6-4C3E-970C-4B1764616F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sales_Raw_Opportunities!$A$3:$J$50</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="290">
   <si>
     <t>SAAFAH — Chairman's Business Review Dashboard</t>
   </si>
@@ -914,18 +914,125 @@
   </si>
   <si>
     <t>Won Date</t>
+  </si>
+  <si>
+    <t>Mentorship Programs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1E4D20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1E4D20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E4D20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFB7950B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -935,94 +1042,14 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF1E4D20"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1E4D20"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1E4D20"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFB7950B"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <sz val="14"/>
+      <color theme="6"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1053,8 +1080,20 @@
         <bgColor rgb="FFFAFAF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFEAF4FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1077,17 +1116,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1095,98 +1147,107 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma 13" xfId="3" xr:uid="{49AD273E-B2B2-4AF1-B521-61793DDE33B6}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 15" xfId="2" xr:uid="{833E9DE7-21A3-43DD-8551-E57B383B4D27}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1457,34 +1518,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
@@ -1547,84 +1608,84 @@
       <c r="F10" s="43"/>
     </row>
     <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
     </row>
     <row r="21" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -1633,12 +1694,12 @@
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
     </row>
     <row r="22" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -1647,12 +1708,12 @@
       <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
     </row>
     <row r="23" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -1661,12 +1722,12 @@
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
     </row>
     <row r="24" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
@@ -1675,12 +1736,12 @@
       <c r="B24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
     </row>
     <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
@@ -1689,12 +1750,12 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
     </row>
     <row r="26" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
@@ -1703,12 +1764,12 @@
       <c r="B26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C26" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -1717,12 +1778,12 @@
       <c r="B27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
@@ -1731,12 +1792,12 @@
       <c r="B28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
     </row>
     <row r="29" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1745,40 +1806,40 @@
       <c r="B29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="44" t="s">
+      <c r="C29" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1787,14 +1848,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="46" t="s">
         <v>48</v>
       </c>
@@ -1804,17 +1865,17 @@
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-    </row>
-    <row r="4" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+    </row>
+    <row r="4" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>50</v>
       </c>
@@ -1828,13 +1889,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="8">
         <f>F11</f>
-        <v>3047377</v>
+        <v>2243750</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>54</v>
@@ -1843,13 +1904,13 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B6" s="8">
         <f>F13</f>
-        <v>1218951</v>
+        <v>936875</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>54</v>
@@ -1858,13 +1919,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="8">
         <f>F16</f>
-        <v>-1951189</v>
+        <v>-1785814.6424999996</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>54</v>
@@ -1873,13 +1934,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="8">
         <f>ABS(F15)</f>
-        <v>3170140</v>
+        <v>2722689.6424999996</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>54</v>
@@ -1888,7 +1949,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>62</v>
       </c>
@@ -1908,80 +1969,83 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B11" s="11">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="C11" s="11">
-        <v>530000</v>
+        <v>330000</v>
       </c>
       <c r="D11" s="11">
-        <v>1043594</v>
+        <v>876750</v>
       </c>
       <c r="E11" s="11">
-        <v>1443783</v>
+        <v>1037000</v>
       </c>
       <c r="F11" s="12">
         <f>SUM(B11:E11)</f>
-        <v>3047377</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2243750</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="11">
-        <v>-18000</v>
-      </c>
-      <c r="C12" s="11">
-        <v>-318000</v>
-      </c>
-      <c r="D12" s="11">
-        <v>-626156</v>
-      </c>
-      <c r="E12" s="11">
-        <v>-866270</v>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>-198000</v>
+      </c>
+      <c r="D12">
+        <v>-507375</v>
+      </c>
+      <c r="E12">
+        <v>-601500</v>
       </c>
       <c r="F12" s="12">
         <f>SUM(B12:E12)</f>
-        <v>-1828426</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-1306875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>70</v>
       </c>
       <c r="B13" s="14">
         <f>B11+B12</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="C13" s="14">
         <f>C11+C12</f>
-        <v>212000</v>
+        <v>132000</v>
       </c>
       <c r="D13" s="14">
         <f>D11+D12</f>
-        <v>417438</v>
+        <v>369375</v>
       </c>
       <c r="E13" s="14">
         <f>E11+E12</f>
-        <v>577513</v>
+        <v>435500</v>
       </c>
       <c r="F13" s="14">
         <f>F11+F12</f>
-        <v>1218951</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>936875</v>
+      </c>
+      <c r="I13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B14" s="15">
         <f>IFERROR(B13/B11,0)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C14" s="15">
         <f>IFERROR(C13/C11,0)</f>
@@ -1989,62 +2053,68 @@
       </c>
       <c r="D14" s="15">
         <f>IFERROR(D13/D11,0)</f>
-        <v>0.40000038329081999</v>
+        <v>0.42130025662959797</v>
       </c>
       <c r="E14" s="15">
         <f>IFERROR(E13/E11,0)</f>
-        <v>0.39999986147502775</v>
+        <v>0.41996142719382834</v>
       </c>
       <c r="F14" s="15">
         <f>IFERROR(F13/F11,0)</f>
-        <v>0.40000006563021245</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0.41754874651810586</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="11">
-        <v>-775035</v>
-      </c>
-      <c r="C15" s="11">
-        <v>-825035</v>
-      </c>
-      <c r="D15" s="11">
-        <v>-775035</v>
-      </c>
-      <c r="E15" s="11">
-        <v>-795035</v>
+      <c r="B15" s="49">
+        <v>-670413.09</v>
+      </c>
+      <c r="C15" s="49">
+        <v>-637944.98583333299</v>
+      </c>
+      <c r="D15" s="49">
+        <v>-656001.89999999991</v>
+      </c>
+      <c r="E15" s="49">
+        <v>-758329.66666666674</v>
       </c>
       <c r="F15" s="12">
         <f>SUM(B15:E15)</f>
-        <v>-3170140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-2722689.6424999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B16" s="14">
         <f>B13+B15</f>
-        <v>-763035</v>
+        <v>-670413.09</v>
       </c>
       <c r="C16" s="14">
         <f>C13+C15</f>
-        <v>-613035</v>
+        <v>-505944.98583333299</v>
       </c>
       <c r="D16" s="14">
         <f>D13+D15</f>
-        <v>-357597</v>
+        <v>-286626.89999999991</v>
       </c>
       <c r="E16" s="14">
         <f>E13+E15</f>
-        <v>-217522</v>
+        <v>-322829.66666666674</v>
       </c>
       <c r="F16" s="14">
         <f>F13+F15</f>
-        <v>-1951189</v>
-      </c>
+        <v>-1785814.6424999996</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2058,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2076,14 +2146,14 @@
       <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="4" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2119,8 +2189,8 @@
         <v>78</v>
       </c>
       <c r="B6" s="8">
-        <f>F14</f>
-        <v>2213344</v>
+        <f>F15</f>
+        <v>1568000</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>54</v>
@@ -2134,8 +2204,8 @@
         <v>80</v>
       </c>
       <c r="B7" s="8">
-        <f>F15+F16</f>
-        <v>-4998566</v>
+        <f>F16+F17</f>
+        <v>-4029564.6424999996</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>54</v>
@@ -2149,8 +2219,8 @@
         <v>82</v>
       </c>
       <c r="B8" s="8">
-        <f>F18</f>
-        <v>-2203767</v>
+        <f>F19</f>
+        <v>-1626047.1424999996</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>54</v>
@@ -2187,16 +2257,16 @@
         <v>581455</v>
       </c>
       <c r="C11" s="12">
-        <f>B18</f>
-        <v>-211580</v>
+        <f>B19</f>
+        <v>-88958.089999999967</v>
       </c>
       <c r="D11" s="12">
-        <f>C18</f>
-        <v>-1046615</v>
+        <f>C19</f>
+        <v>-736903.07583333296</v>
       </c>
       <c r="E11" s="12">
-        <f>D18</f>
-        <v>-1760306</v>
+        <f>D19</f>
+        <v>-1293092.4758333329</v>
       </c>
       <c r="F11" s="12">
         <f>B11</f>
@@ -2208,199 +2278,201 @@
         <v>84</v>
       </c>
       <c r="B12" s="8">
-        <f>Pipeline_Revenue!B28</f>
         <v>0</v>
       </c>
       <c r="C12" s="8">
-        <f>Pipeline_Revenue!C28</f>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="D12" s="8">
-        <f>Pipeline_Revenue!D28</f>
-        <v>421125</v>
+        <v>400000</v>
       </c>
       <c r="E12" s="8">
-        <f>Pipeline_Revenue!E28</f>
-        <v>778183</v>
+        <v>560000</v>
       </c>
       <c r="F12" s="12">
         <f>SUM(B12:E12)</f>
-        <v>1229308</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8">
+        <v>57187.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>196875</v>
+      </c>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="8">
-        <f>Pipeline_Revenue!B29</f>
+      <c r="B14" s="8">
         <v>0</v>
       </c>
-      <c r="C13" s="8">
-        <f>Pipeline_Revenue!C29</f>
-        <v>278000</v>
-      </c>
-      <c r="D13" s="8">
-        <f>Pipeline_Revenue!D29</f>
-        <v>266375</v>
-      </c>
-      <c r="E13" s="8">
-        <f>Pipeline_Revenue!E29</f>
-        <v>439661</v>
-      </c>
-      <c r="F13" s="12">
-        <f>SUM(B13:E13)</f>
-        <v>984036</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="C14" s="8">
+        <v>188000</v>
+      </c>
+      <c r="D14" s="8">
+        <v>150000</v>
+      </c>
+      <c r="E14" s="8">
+        <v>270000</v>
+      </c>
+      <c r="F14" s="12">
+        <f>SUM(B14:E14)</f>
+        <v>608000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="14">
-        <f>B12+B13</f>
+      <c r="B15" s="14">
+        <f>SUM(B12:B14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="14">
-        <f>C12+C13</f>
-        <v>308000</v>
-      </c>
-      <c r="D14" s="14">
-        <f>D12+D13</f>
-        <v>687500</v>
-      </c>
-      <c r="E14" s="14">
-        <f>E12+E13</f>
-        <v>1217844</v>
-      </c>
-      <c r="F14" s="14">
-        <f>F12+F13</f>
-        <v>2213344</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="8">
-        <f>Financial_Overview!B12</f>
-        <v>-18000</v>
-      </c>
-      <c r="C15" s="8">
-        <f>Financial_Overview!C12</f>
-        <v>-318000</v>
-      </c>
-      <c r="D15" s="8">
-        <f>Financial_Overview!D12</f>
-        <v>-626156</v>
-      </c>
-      <c r="E15" s="8">
-        <f>Financial_Overview!E12</f>
-        <v>-866270</v>
-      </c>
-      <c r="F15" s="8">
-        <f>Financial_Overview!F12</f>
-        <v>-1828426</v>
+      <c r="C15" s="14">
+        <f t="shared" ref="C15:E15" si="0">SUM(C12:C14)</f>
+        <v>188000</v>
+      </c>
+      <c r="D15" s="14">
+        <f t="shared" si="0"/>
+        <v>607187.5</v>
+      </c>
+      <c r="E15" s="14">
+        <f t="shared" si="0"/>
+        <v>1026875</v>
+      </c>
+      <c r="F15" s="14">
+        <f>F12+F14</f>
+        <v>1568000</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-198000</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-507375</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-601500</v>
+      </c>
+      <c r="F16" s="8">
+        <f>Financial_Overview!F12</f>
+        <v>-1306875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B17" s="8">
         <f>Financial_Overview!B15</f>
-        <v>-775035</v>
-      </c>
-      <c r="C16" s="8">
+        <v>-670413.09</v>
+      </c>
+      <c r="C17" s="8">
         <f>Financial_Overview!C15</f>
-        <v>-825035</v>
-      </c>
-      <c r="D16" s="8">
+        <v>-637944.98583333299</v>
+      </c>
+      <c r="D17" s="8">
         <f>Financial_Overview!D15</f>
-        <v>-775035</v>
-      </c>
-      <c r="E16" s="8">
+        <v>-656001.89999999991</v>
+      </c>
+      <c r="E17" s="8">
         <f>Financial_Overview!E15</f>
-        <v>-795035</v>
-      </c>
-      <c r="F16" s="8">
+        <v>-758329.66666666674</v>
+      </c>
+      <c r="F17" s="8">
         <f>Financial_Overview!F15</f>
-        <v>-3170140</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="14">
-        <f>B14+B15+B16</f>
-        <v>-793035</v>
-      </c>
-      <c r="C17" s="14">
-        <f>C14+C15+C16</f>
-        <v>-835035</v>
-      </c>
-      <c r="D17" s="14">
-        <f>D14+D15+D16</f>
-        <v>-713691</v>
-      </c>
-      <c r="E17" s="14">
-        <f>E14+E15+E16</f>
-        <v>-443461</v>
-      </c>
-      <c r="F17" s="14">
-        <f>F14+F15+F16</f>
-        <v>-2785222</v>
+        <v>-2722689.6424999996</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="14">
+        <f>B15+B16+B17</f>
+        <v>-670413.09</v>
+      </c>
+      <c r="C18" s="14">
+        <f t="shared" ref="C18:E18" si="1">C15+C16+C17</f>
+        <v>-647944.98583333299</v>
+      </c>
+      <c r="D18" s="14">
+        <f t="shared" si="1"/>
+        <v>-556189.39999999991</v>
+      </c>
+      <c r="E18" s="14">
+        <f t="shared" si="1"/>
+        <v>-332954.66666666674</v>
+      </c>
+      <c r="F18" s="14">
+        <f>F15+F16+F17</f>
+        <v>-2461564.6424999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="14">
-        <f>B11+B17</f>
-        <v>-211580</v>
-      </c>
-      <c r="C18" s="14">
-        <f>C11+C17</f>
-        <v>-1046615</v>
-      </c>
-      <c r="D18" s="14">
-        <f>D11+D17</f>
-        <v>-1760306</v>
-      </c>
-      <c r="E18" s="14">
-        <f>E11+E17</f>
-        <v>-2203767</v>
-      </c>
-      <c r="F18" s="14">
-        <f>E18</f>
-        <v>-2203767</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+      <c r="B19" s="50">
+        <f>B18+B11</f>
+        <v>-88958.089999999967</v>
+      </c>
+      <c r="C19" s="50">
+        <f t="shared" ref="C19:E19" si="2">C18+C11</f>
+        <v>-736903.07583333296</v>
+      </c>
+      <c r="D19" s="50">
+        <f t="shared" si="2"/>
+        <v>-1293092.4758333329</v>
+      </c>
+      <c r="E19" s="50">
+        <f t="shared" si="2"/>
+        <v>-1626047.1424999996</v>
+      </c>
+      <c r="F19" s="14">
+        <f>E19</f>
+        <v>-1626047.1424999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="12">
-        <f>IF(B18&lt;0,B18,0)</f>
-        <v>-211580</v>
-      </c>
-      <c r="C19" s="12">
-        <f>IF(C18&lt;0,C18,0)</f>
-        <v>-1046615</v>
-      </c>
-      <c r="D19" s="12">
-        <f>IF(D18&lt;0,D18,0)</f>
-        <v>-1760306</v>
-      </c>
-      <c r="E19" s="12">
-        <f>IF(E18&lt;0,E18,0)</f>
-        <v>-2203767</v>
-      </c>
-      <c r="F19" s="12">
-        <f>E19</f>
-        <v>-2203767</v>
+      <c r="B20" s="12">
+        <f>IF(B19&lt;0,B19,0)</f>
+        <v>-88958.089999999967</v>
+      </c>
+      <c r="C20" s="12">
+        <f>IF(C19&lt;0,C19,0)</f>
+        <v>-736903.07583333296</v>
+      </c>
+      <c r="D20" s="12">
+        <f>IF(D19&lt;0,D19,0)</f>
+        <v>-1293092.4758333329</v>
+      </c>
+      <c r="E20" s="12">
+        <f>IF(E19&lt;0,E19,0)</f>
+        <v>-1626047.1424999996</v>
+      </c>
+      <c r="F20" s="12">
+        <f>E20</f>
+        <v>-1626047.1424999996</v>
       </c>
     </row>
   </sheetData>
@@ -2415,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2437,17 +2509,17 @@
       <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="4" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2460,7 +2532,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -2841,24 +2913,24 @@
         <v>127</v>
       </c>
       <c r="B27" s="14">
-        <f>B28+B29</f>
+        <f>B28+B30</f>
         <v>0</v>
       </c>
       <c r="C27" s="14">
-        <f>C28+C29</f>
-        <v>308000</v>
+        <f>C28+C30</f>
+        <v>240000</v>
       </c>
       <c r="D27" s="14">
-        <f>D28+D29</f>
-        <v>687500</v>
+        <f>D28+D30</f>
+        <v>666750</v>
       </c>
       <c r="E27" s="14">
-        <f>E28+E29</f>
-        <v>1217844</v>
+        <f>E28+E30</f>
+        <v>767000</v>
       </c>
       <c r="F27" s="14">
-        <f>F28+F29</f>
-        <v>2213344</v>
+        <f>F28+F30</f>
+        <v>1673750</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -2869,38 +2941,57 @@
         <v>0</v>
       </c>
       <c r="C28" s="11">
-        <v>30000</v>
+        <v>240000</v>
       </c>
       <c r="D28" s="11">
-        <v>421125</v>
+        <v>480000</v>
       </c>
       <c r="E28" s="11">
-        <v>778183</v>
+        <v>560000</v>
       </c>
       <c r="F28" s="12">
         <f>SUM(B28:E28)</f>
-        <v>1229308</v>
+        <v>1280000</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11">
+        <v>90000</v>
+      </c>
+      <c r="D29" s="11">
+        <v>210000</v>
+      </c>
+      <c r="E29" s="11">
+        <v>270000</v>
+      </c>
+      <c r="F29" s="12">
+        <f t="shared" ref="F29:F30" si="1">SUM(B29:E29)</f>
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B30" s="11">
         <v>0</v>
       </c>
-      <c r="C29" s="11">
-        <v>278000</v>
-      </c>
-      <c r="D29" s="11">
-        <v>266375</v>
-      </c>
-      <c r="E29" s="11">
-        <v>439661</v>
-      </c>
-      <c r="F29" s="12">
-        <f>SUM(B29:E29)</f>
-        <v>984036</v>
+      <c r="C30" s="11">
+        <v>0</v>
+      </c>
+      <c r="D30" s="11">
+        <v>186750</v>
+      </c>
+      <c r="E30" s="11">
+        <v>207000</v>
+      </c>
+      <c r="F30" s="12">
+        <f t="shared" si="1"/>
+        <v>393750</v>
       </c>
     </row>
   </sheetData>
@@ -2942,17 +3033,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="4" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4311,15 +4402,15 @@
       <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4607,11 +4698,11 @@
       <c r="C1" s="46"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -4811,15 +4902,15 @@
       <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\safa update\12.05.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05A7B63F-87D6-4C3E-970C-4B1764616F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEE47D0-AB87-43A7-BC24-19F17130B649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="292">
   <si>
     <t>SAAFAH — Chairman's Business Review Dashboard</t>
   </si>
@@ -917,6 +917,12 @@
   </si>
   <si>
     <t>Mentorship Programs</t>
+  </si>
+  <si>
+    <t>Mentorship Program Revenue</t>
+  </si>
+  <si>
+    <t>Dec</t>
   </si>
 </sst>
 </file>
@@ -1895,7 +1901,7 @@
       </c>
       <c r="B5" s="8">
         <f>F11</f>
-        <v>2243750</v>
+        <v>2273750</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>54</v>
@@ -1910,7 +1916,7 @@
       </c>
       <c r="B6" s="8">
         <f>F13</f>
-        <v>936875</v>
+        <v>948875</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>54</v>
@@ -1925,7 +1931,7 @@
       </c>
       <c r="B7" s="8">
         <f>F16</f>
-        <v>-1785814.6424999996</v>
+        <v>-1773814.6425000001</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>54</v>
@@ -1940,7 +1946,7 @@
       </c>
       <c r="B8" s="8">
         <f>ABS(F15)</f>
-        <v>2722689.6424999996</v>
+        <v>2722689.6425000001</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>54</v>
@@ -1980,14 +1986,14 @@
         <v>330000</v>
       </c>
       <c r="D11" s="11">
-        <v>876750</v>
+        <v>906750</v>
       </c>
       <c r="E11" s="11">
         <v>1037000</v>
       </c>
       <c r="F11" s="12">
         <f>SUM(B11:E11)</f>
-        <v>2243750</v>
+        <v>2273750</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -2001,14 +2007,14 @@
         <v>-198000</v>
       </c>
       <c r="D12">
-        <v>-507375</v>
+        <v>-525375</v>
       </c>
       <c r="E12">
         <v>-601500</v>
       </c>
       <c r="F12" s="12">
         <f>SUM(B12:E12)</f>
-        <v>-1306875</v>
+        <v>-1324875</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -2025,7 +2031,7 @@
       </c>
       <c r="D13" s="14">
         <f>D11+D12</f>
-        <v>369375</v>
+        <v>381375</v>
       </c>
       <c r="E13" s="14">
         <f>E11+E12</f>
@@ -2033,7 +2039,7 @@
       </c>
       <c r="F13" s="14">
         <f>F11+F12</f>
-        <v>936875</v>
+        <v>948875</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -2053,7 +2059,7 @@
       </c>
       <c r="D14" s="15">
         <f>IFERROR(D13/D11,0)</f>
-        <v>0.42130025662959797</v>
+        <v>0.42059553349875928</v>
       </c>
       <c r="E14" s="15">
         <f>IFERROR(E13/E11,0)</f>
@@ -2061,7 +2067,7 @@
       </c>
       <c r="F14" s="15">
         <f>IFERROR(F13/F11,0)</f>
-        <v>0.41754874651810586</v>
+        <v>0.41731720725673449</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -2075,14 +2081,14 @@
         <v>-637944.98583333299</v>
       </c>
       <c r="D15" s="49">
-        <v>-656001.89999999991</v>
+        <v>-656001.9</v>
       </c>
       <c r="E15" s="49">
-        <v>-758329.66666666674</v>
+        <v>-758329.66666666698</v>
       </c>
       <c r="F15" s="12">
         <f>SUM(B15:E15)</f>
-        <v>-2722689.6424999996</v>
+        <v>-2722689.6425000001</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -2099,15 +2105,15 @@
       </c>
       <c r="D16" s="14">
         <f>D13+D15</f>
-        <v>-286626.89999999991</v>
+        <v>-274626.90000000002</v>
       </c>
       <c r="E16" s="14">
         <f>E13+E15</f>
-        <v>-322829.66666666674</v>
+        <v>-322829.66666666698</v>
       </c>
       <c r="F16" s="14">
         <f>F13+F15</f>
-        <v>-1785814.6424999996</v>
+        <v>-1773814.6425000001</v>
       </c>
     </row>
     <row r="21" spans="4:7" ht="18" x14ac:dyDescent="0.35">
@@ -2175,7 +2181,7 @@
       </c>
       <c r="B5" s="8">
         <f>B11</f>
-        <v>581455</v>
+        <v>581455.34000000008</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>54</v>
@@ -2190,7 +2196,7 @@
       </c>
       <c r="B6" s="8">
         <f>F15</f>
-        <v>1568000</v>
+        <v>1822062.5</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>54</v>
@@ -2205,7 +2211,7 @@
       </c>
       <c r="B7" s="8">
         <f>F16+F17</f>
-        <v>-4029564.6424999996</v>
+        <v>-4047564.6425000001</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>54</v>
@@ -2220,7 +2226,7 @@
       </c>
       <c r="B8" s="8">
         <f>F19</f>
-        <v>-1626047.1424999996</v>
+        <v>-1644046.8024999998</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>54</v>
@@ -2254,23 +2260,20 @@
         <v>76</v>
       </c>
       <c r="B11" s="11">
-        <v>581455</v>
+        <v>581455.34000000008</v>
       </c>
       <c r="C11" s="12">
-        <f>B19</f>
-        <v>-88958.089999999967</v>
+        <v>-88957.749999999884</v>
       </c>
       <c r="D11" s="12">
-        <f>C19</f>
-        <v>-736903.07583333296</v>
+        <v>-736902.73583333287</v>
       </c>
       <c r="E11" s="12">
-        <f>D19</f>
-        <v>-1293092.4758333329</v>
+        <v>-1311092.1358333328</v>
       </c>
       <c r="F11" s="12">
         <f>B11</f>
-        <v>581455</v>
+        <v>581455.34000000008</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2298,15 +2301,22 @@
       <c r="A13" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="B13" s="8">
+        <v>0</v>
+      </c>
+      <c r="C13" s="8">
+        <v>188000</v>
+      </c>
       <c r="D13" s="8">
-        <v>57187.5</v>
+        <v>150000</v>
       </c>
       <c r="E13" s="8">
-        <v>196875</v>
-      </c>
-      <c r="F13" s="12"/>
+        <v>270000</v>
+      </c>
+      <c r="F13" s="12">
+        <f>SUM(B13:E13)</f>
+        <v>608000</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -2316,21 +2326,21 @@
         <v>0</v>
       </c>
       <c r="C14" s="8">
-        <v>188000</v>
+        <v>0</v>
       </c>
       <c r="D14" s="8">
-        <v>150000</v>
+        <v>57187.5</v>
       </c>
       <c r="E14" s="8">
-        <v>270000</v>
+        <v>196875</v>
       </c>
       <c r="F14" s="12">
         <f>SUM(B14:E14)</f>
-        <v>608000</v>
+        <v>254062.5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="14" t="s">
         <v>78</v>
       </c>
       <c r="B15" s="14">
@@ -2350,8 +2360,8 @@
         <v>1026875</v>
       </c>
       <c r="F15" s="14">
-        <f>F12+F14</f>
-        <v>1568000</v>
+        <f>F12+F14+F13</f>
+        <v>1822062.5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2372,7 +2382,7 @@
       </c>
       <c r="F16" s="8">
         <f>Financial_Overview!F12</f>
-        <v>-1306875</v>
+        <v>-1324875</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2389,15 +2399,15 @@
       </c>
       <c r="D17" s="8">
         <f>Financial_Overview!D15</f>
-        <v>-656001.89999999991</v>
+        <v>-656001.9</v>
       </c>
       <c r="E17" s="8">
         <f>Financial_Overview!E15</f>
-        <v>-758329.66666666674</v>
+        <v>-758329.66666666698</v>
       </c>
       <c r="F17" s="8">
         <f>Financial_Overview!F15</f>
-        <v>-2722689.6424999996</v>
+        <v>-2722689.6425000001</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2414,15 +2424,15 @@
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>-556189.39999999991</v>
+        <v>-556189.4</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="1"/>
-        <v>-332954.66666666674</v>
+        <v>-332954.66666666698</v>
       </c>
       <c r="F18" s="14">
         <f>F15+F16+F17</f>
-        <v>-2461564.6424999996</v>
+        <v>-2225502.1425000001</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2431,23 +2441,23 @@
       </c>
       <c r="B19" s="50">
         <f>B18+B11</f>
-        <v>-88958.089999999967</v>
+        <v>-88957.749999999884</v>
       </c>
       <c r="C19" s="50">
         <f t="shared" ref="C19:E19" si="2">C18+C11</f>
-        <v>-736903.07583333296</v>
+        <v>-736902.73583333287</v>
       </c>
       <c r="D19" s="50">
         <f t="shared" si="2"/>
-        <v>-1293092.4758333329</v>
+        <v>-1293092.1358333328</v>
       </c>
       <c r="E19" s="50">
         <f t="shared" si="2"/>
-        <v>-1626047.1424999996</v>
+        <v>-1644046.8024999998</v>
       </c>
       <c r="F19" s="14">
         <f>E19</f>
-        <v>-1626047.1424999996</v>
+        <v>-1644046.8024999998</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2456,23 +2466,23 @@
       </c>
       <c r="B20" s="12">
         <f>IF(B19&lt;0,B19,0)</f>
-        <v>-88958.089999999967</v>
+        <v>-88957.749999999884</v>
       </c>
       <c r="C20" s="12">
         <f>IF(C19&lt;0,C19,0)</f>
-        <v>-736903.07583333296</v>
+        <v>-736902.73583333287</v>
       </c>
       <c r="D20" s="12">
         <f>IF(D19&lt;0,D19,0)</f>
-        <v>-1293092.4758333329</v>
+        <v>-1293092.1358333328</v>
       </c>
       <c r="E20" s="12">
         <f>IF(E19&lt;0,E19,0)</f>
-        <v>-1626047.1424999996</v>
+        <v>-1644046.8024999998</v>
       </c>
       <c r="F20" s="12">
         <f>E20</f>
-        <v>-1626047.1424999996</v>
+        <v>-1644046.8024999998</v>
       </c>
     </row>
   </sheetData>
@@ -2487,15 +2497,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="8" width="17" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="46" t="s">
         <v>89</v>
       </c>
@@ -2508,7 +2520,7 @@
       <c r="H1" s="46"/>
       <c r="I1" s="46"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="45" t="s">
         <v>90</v>
       </c>
@@ -2521,7 +2533,7 @@
       <c r="H2" s="45"/>
       <c r="I2" s="45"/>
     </row>
-    <row r="4" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>91</v>
       </c>
@@ -2532,43 +2544,43 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B5" s="8">
-        <f>D23</f>
-        <v>2543620</v>
+        <f>E24</f>
+        <v>1822062.5</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B6" s="12">
-        <f>SUMIFS(G12:G22,E12:E22,"Q1")+SUMIFS(G12:G22,E12:E22,"Q2")</f>
+        <f>SUMIFS(H12:H22,F12:F22,"Q1")+SUMIFS(H12:H22,F12:F22,"Q2")</f>
         <v>1970000</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B7" s="12">
-        <f>COUNTA(F12:F22)</f>
+        <f>COUNTA(G12:G22)</f>
         <v>9</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>98</v>
       </c>
@@ -2578,420 +2590,557 @@
       <c r="C10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12">
+        <f>B12+C12+D12</f>
         <v>0</v>
       </c>
-      <c r="C12" s="11">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <f t="shared" ref="D12:D22" si="0">B12+C12</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="F12" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="G12" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="G12" s="11">
+      <c r="H12" s="11">
         <v>500000</v>
       </c>
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12">
+        <f t="shared" ref="E13:E23" si="0">B13+C13+D13</f>
         <v>0</v>
       </c>
-      <c r="C13" s="11">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="F13" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="11">
+        <v>500000</v>
+      </c>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="F14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="11">
-        <v>500000</v>
-      </c>
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="11">
-        <v>0</v>
-      </c>
-      <c r="C14" s="11">
-        <v>30000</v>
-      </c>
-      <c r="D14" s="12">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="18" t="s">
+      <c r="G14" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="11">
+      <c r="H14" s="11">
         <v>350000</v>
       </c>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C15" s="11">
-        <v>90000</v>
-      </c>
-      <c r="D15" s="12">
-        <f t="shared" si="0"/>
-        <v>90000</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="F15" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="G15" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="11">
+      <c r="H15" s="11">
         <v>330000</v>
       </c>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="11">
-        <v>100000</v>
-      </c>
-      <c r="C16" s="11">
-        <v>40000</v>
-      </c>
-      <c r="D16" s="12">
+      <c r="B16">
+        <v>80000</v>
+      </c>
+      <c r="C16">
+        <v>86250</v>
+      </c>
+      <c r="E16" s="12">
         <f t="shared" si="0"/>
-        <v>140000</v>
-      </c>
-      <c r="E16" s="17" t="s">
+        <v>166250</v>
+      </c>
+      <c r="F16" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="G16" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="11">
+      <c r="H16" s="11">
         <v>220000</v>
       </c>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="11">
-        <v>185000</v>
-      </c>
-      <c r="C17" s="11">
-        <v>115000</v>
-      </c>
-      <c r="D17" s="12">
+      <c r="B17">
+        <v>160000</v>
+      </c>
+      <c r="C17">
+        <v>101750</v>
+      </c>
+      <c r="E17" s="12">
         <f t="shared" si="0"/>
-        <v>300000</v>
-      </c>
-      <c r="E17" s="17" t="s">
+        <v>261750</v>
+      </c>
+      <c r="F17" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="11">
+      <c r="H17" s="11">
         <v>70000</v>
       </c>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="11">
-        <v>136125</v>
-      </c>
-      <c r="C18" s="11">
-        <v>111375</v>
-      </c>
-      <c r="D18" s="12">
+      <c r="B18">
+        <v>160000</v>
+      </c>
+      <c r="C18">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="12">
         <f t="shared" si="0"/>
-        <v>247500</v>
-      </c>
-      <c r="E18" s="17" t="s">
+        <v>190000</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="G18" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="11">
+      <c r="H18" s="11">
         <v>50000</v>
       </c>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="18"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="11">
-        <v>170156</v>
-      </c>
-      <c r="C19" s="11">
-        <v>139219</v>
-      </c>
-      <c r="D19" s="12">
+      <c r="B19">
+        <v>160000</v>
+      </c>
+      <c r="C19">
+        <v>60000</v>
+      </c>
+      <c r="E19" s="12">
         <f t="shared" si="0"/>
-        <v>309375</v>
-      </c>
-      <c r="E19" s="17" t="s">
+        <v>220000</v>
+      </c>
+      <c r="F19" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="G19" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="11">
+      <c r="H19" s="11">
         <v>45000</v>
       </c>
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="18"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="11">
-        <v>331064</v>
-      </c>
-      <c r="C20" s="11">
-        <v>155655</v>
-      </c>
-      <c r="D20" s="12">
+      <c r="B20">
+        <v>160000</v>
+      </c>
+      <c r="C20">
+        <v>60000</v>
+      </c>
+      <c r="D20">
+        <v>57187.5</v>
+      </c>
+      <c r="E20" s="12">
         <f t="shared" si="0"/>
-        <v>486719</v>
-      </c>
-      <c r="E20" s="17" t="s">
+        <v>277187.5</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="G20" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="G20" s="11">
+      <c r="H20" s="11">
         <v>30000</v>
       </c>
-      <c r="H20" s="18"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="18"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="11">
-        <v>276963</v>
-      </c>
-      <c r="C21" s="11">
-        <v>144788</v>
-      </c>
-      <c r="D21" s="12">
+      <c r="B21">
+        <v>240000</v>
+      </c>
+      <c r="C21">
+        <v>90000</v>
+      </c>
+      <c r="D21">
+        <v>62250</v>
+      </c>
+      <c r="E21" s="12">
         <f t="shared" si="0"/>
-        <v>421751</v>
-      </c>
-      <c r="E21" s="17" t="s">
+        <v>392250</v>
+      </c>
+      <c r="F21" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="18"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G21" s="18"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B22" s="11">
-        <v>330051</v>
-      </c>
-      <c r="C22" s="11">
-        <v>188224</v>
-      </c>
-      <c r="D22" s="12">
+      <c r="C22">
+        <v>90000</v>
+      </c>
+      <c r="D22">
+        <v>67312.5</v>
+      </c>
+      <c r="E22" s="12">
         <f t="shared" si="0"/>
-        <v>518275</v>
-      </c>
-      <c r="E22" s="17" t="s">
+        <v>157312.5</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="18"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+      <c r="G22" s="18"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="18"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C23">
+        <v>90000</v>
+      </c>
+      <c r="D23">
+        <v>67312.5</v>
+      </c>
+      <c r="E23" s="12">
+        <f t="shared" si="0"/>
+        <v>157312.5</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="18"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="18"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="14">
-        <f>SUM(B12:B22)</f>
-        <v>1529359</v>
-      </c>
-      <c r="C23" s="14">
-        <f>SUM(C12:C22)</f>
-        <v>1014261</v>
-      </c>
-      <c r="D23" s="14">
-        <f>SUM(D12:D22)</f>
-        <v>2543620</v>
-      </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="14">
-        <f>SUM(G12:G22)</f>
+      <c r="B24" s="14">
+        <f>SUM(B12:B23)</f>
+        <v>960000</v>
+      </c>
+      <c r="C24" s="14">
+        <f t="shared" ref="C24:D24" si="1">SUM(C12:C23)</f>
+        <v>608000</v>
+      </c>
+      <c r="D24" s="14">
+        <f t="shared" si="1"/>
+        <v>254062.5</v>
+      </c>
+      <c r="E24" s="14">
+        <f>SUM(E12:E23)</f>
+        <v>1822062.5</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="14">
+        <f>SUM(H12:H22)</f>
         <v>2095000</v>
       </c>
-      <c r="H23" s="21"/>
-    </row>
-    <row r="26" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="I24" s="21"/>
+    </row>
+    <row r="27" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="14">
-        <f>B28+B30</f>
+      <c r="B28" s="14">
+        <f>B29+B31</f>
         <v>0</v>
       </c>
-      <c r="C27" s="14">
-        <f>C28+C30</f>
+      <c r="C28" s="14">
+        <f>C29+C31</f>
+        <v>428000</v>
+      </c>
+      <c r="D28" s="14">
+        <f>D29+D31</f>
+        <v>630000</v>
+      </c>
+      <c r="E28" s="14">
+        <f>E29+E31</f>
+        <v>510000</v>
+      </c>
+      <c r="F28" s="14">
+        <f>F29+F31+F30</f>
+        <v>1822062.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="11">
+        <v>0</v>
+      </c>
+      <c r="C29" s="11">
+        <f>SUM(B15:B17)</f>
         <v>240000</v>
       </c>
-      <c r="D27" s="14">
-        <f>D28+D30</f>
-        <v>666750</v>
-      </c>
-      <c r="E27" s="14">
-        <f>E28+E30</f>
-        <v>767000</v>
-      </c>
-      <c r="F27" s="14">
-        <f>F28+F30</f>
-        <v>1673750</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="11">
+      <c r="D29" s="11">
+        <f>SUM(B18:B20)</f>
+        <v>480000</v>
+      </c>
+      <c r="E29" s="11">
+        <f>SUM(B21:B23)</f>
+        <v>240000</v>
+      </c>
+      <c r="F29" s="12">
+        <f>SUM(B29:E29)</f>
+        <v>960000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11">
+        <f>SUM(D15:D17)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="11">
+      <c r="D30" s="11">
+        <f>SUM(D18:D20)</f>
+        <v>57187.5</v>
+      </c>
+      <c r="E30" s="11">
+        <f>SUM(D21:D23)</f>
+        <v>196875</v>
+      </c>
+      <c r="F30" s="12">
+        <f t="shared" ref="F30:F31" si="2">SUM(B30:E30)</f>
+        <v>254062.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="11">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11">
+        <f>SUM(C15:C17)</f>
+        <v>188000</v>
+      </c>
+      <c r="D31" s="11">
+        <f>SUM(C18:C20)</f>
+        <v>150000</v>
+      </c>
+      <c r="E31" s="11">
+        <f>SUM(C21:C23)</f>
+        <v>270000</v>
+      </c>
+      <c r="F31" s="12">
+        <f t="shared" si="2"/>
+        <v>608000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>80000</v>
+      </c>
+      <c r="C37">
+        <v>86250</v>
+      </c>
+      <c r="D37">
+        <v>57187.5</v>
+      </c>
+      <c r="E37">
+        <v>86250</v>
+      </c>
+      <c r="F37">
+        <v>101750</v>
+      </c>
+      <c r="G37">
+        <v>30000</v>
+      </c>
+      <c r="H37">
+        <v>60000</v>
+      </c>
+      <c r="I37">
+        <v>60000</v>
+      </c>
+      <c r="J37">
+        <v>90000</v>
+      </c>
+      <c r="K37">
+        <v>90000</v>
+      </c>
+      <c r="L37">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>160000</v>
+      </c>
+      <c r="C38">
+        <v>101750</v>
+      </c>
+      <c r="D38">
+        <v>62250</v>
+      </c>
+      <c r="E38">
+        <v>57187.5</v>
+      </c>
+      <c r="F38">
+        <v>62250</v>
+      </c>
+      <c r="G38">
+        <v>67312.5</v>
+      </c>
+      <c r="H38">
+        <v>67312.5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>160000</v>
+      </c>
+      <c r="C39">
+        <v>30000</v>
+      </c>
+      <c r="D39">
+        <v>67312.5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>160000</v>
+      </c>
+      <c r="C40">
+        <v>60000</v>
+      </c>
+      <c r="D40">
+        <v>67312.5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>160000</v>
+      </c>
+      <c r="C41">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B42">
         <v>240000</v>
       </c>
-      <c r="D28" s="11">
-        <v>480000</v>
-      </c>
-      <c r="E28" s="11">
-        <v>560000</v>
-      </c>
-      <c r="F28" s="12">
-        <f>SUM(B28:E28)</f>
-        <v>1280000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11">
+      <c r="C42">
         <v>90000</v>
       </c>
-      <c r="D29" s="11">
-        <v>210000</v>
-      </c>
-      <c r="E29" s="11">
-        <v>270000</v>
-      </c>
-      <c r="F29" s="12">
-        <f t="shared" ref="F29:F30" si="1">SUM(B29:E29)</f>
-        <v>570000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" s="11">
-        <v>0</v>
-      </c>
-      <c r="C30" s="11">
-        <v>0</v>
-      </c>
-      <c r="D30" s="11">
-        <v>186750</v>
-      </c>
-      <c r="E30" s="11">
-        <v>207000</v>
-      </c>
-      <c r="F30" s="12">
-        <f t="shared" si="1"/>
-        <v>393750</v>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C43">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C44">
+        <v>90000</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\safa update\12.05.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEE47D0-AB87-43A7-BC24-19F17130B649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC72A9AC-3B8F-4820-9E93-E6CDDF8EDE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Strategy_Operations" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sales_Raw_Opportunities!$A$3:$J$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sales_Raw_Opportunities!$A$3:$J$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="289">
   <si>
     <t>SAAFAH — Chairman's Business Review Dashboard</t>
   </si>
@@ -691,27 +691,15 @@
     <t>SABIC</t>
   </si>
   <si>
-    <t>Amaal Fathani</t>
-  </si>
-  <si>
-    <t>Milaf ( PIF)</t>
-  </si>
-  <si>
     <t>Kaplan</t>
   </si>
   <si>
-    <t>National Company for Mechanichal Systems(NCMS)</t>
-  </si>
-  <si>
     <t>CMA(Fintech)</t>
   </si>
   <si>
     <t>Avilease</t>
   </si>
   <si>
-    <t>الشركة الوطنية للأنظمة الميكانيكية</t>
-  </si>
-  <si>
     <t xml:space="preserve">Saudi Global Ports </t>
   </si>
   <si>
@@ -721,18 +709,9 @@
     <t>MEP Sustanability Champion Support</t>
   </si>
   <si>
-    <t xml:space="preserve">University Partnership </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentorship &amp; ESG Training </t>
-  </si>
-  <si>
     <t>ESG Training Certification Partnership</t>
   </si>
   <si>
-    <t>Coperate Governance Model</t>
-  </si>
-  <si>
     <t>Supporting Fentec Saudi on Sustainable Investment</t>
   </si>
   <si>
@@ -823,9 +802,6 @@
     <t>KPMG</t>
   </si>
   <si>
-    <t>EY</t>
-  </si>
-  <si>
     <t>NCFB</t>
   </si>
   <si>
@@ -898,9 +874,6 @@
     <t>Gihan Hyde</t>
   </si>
   <si>
-    <t xml:space="preserve"> -   </t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -923,6 +896,25 @@
   </si>
   <si>
     <t>Dec</t>
+  </si>
+  <si>
+    <t>The National Company for Mechanical Systems (NCMS) 
+الشركة الوطنية للأنظمة الميكانيكية</t>
+  </si>
+  <si>
+    <t>Governance Framework Advisory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savvy Group ( PIF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentorship </t>
+  </si>
+  <si>
+    <t xml:space="preserve">april 26th </t>
+  </si>
+  <si>
+    <t>On hold</t>
   </si>
 </sst>
 </file>
@@ -934,7 +926,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -1229,25 +1221,25 @@
     <xf numFmtId="166" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1524,174 +1516,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
     </row>
     <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
     </row>
     <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
     </row>
     <row r="21" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -1700,12 +1692,12 @@
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
     </row>
     <row r="22" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -1714,12 +1706,12 @@
       <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -1728,12 +1720,12 @@
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
@@ -1742,12 +1734,12 @@
       <c r="B24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
@@ -1756,12 +1748,12 @@
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
     </row>
     <row r="26" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
@@ -1770,12 +1762,12 @@
       <c r="B26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -1784,12 +1776,12 @@
       <c r="B27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
     </row>
     <row r="28" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
@@ -1798,12 +1790,12 @@
       <c r="B28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
     </row>
     <row r="29" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1812,40 +1804,40 @@
       <c r="B29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1862,24 +1854,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="4" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2074,16 +2066,16 @@
       <c r="A15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="49">
+      <c r="B15" s="41">
         <v>-670413.09</v>
       </c>
-      <c r="C15" s="49">
+      <c r="C15" s="41">
         <v>-637944.98583333299</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="41">
         <v>-656001.9</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="41">
         <v>-758329.66666666698</v>
       </c>
       <c r="F15" s="12">
@@ -2117,10 +2109,10 @@
       </c>
     </row>
     <row r="21" spans="4:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2142,24 +2134,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="4" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2299,7 +2291,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B13" s="8">
         <v>0</v>
@@ -2439,19 +2431,19 @@
       <c r="A19" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="50">
+      <c r="B19" s="42">
         <f>B18+B11</f>
         <v>-88957.749999999884</v>
       </c>
-      <c r="C19" s="50">
+      <c r="C19" s="42">
         <f t="shared" ref="C19:E19" si="2">C18+C11</f>
         <v>-736902.73583333287</v>
       </c>
-      <c r="D19" s="50">
+      <c r="D19" s="42">
         <f t="shared" si="2"/>
         <v>-1293092.1358333328</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="42">
         <f t="shared" si="2"/>
         <v>-1644046.8024999998</v>
       </c>
@@ -2508,30 +2500,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="4" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2544,7 +2536,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -2591,7 +2583,7 @@
         <v>100</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>101</v>
@@ -2750,7 +2742,7 @@
       </c>
       <c r="I17" s="18"/>
     </row>
-    <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>118</v>
       </c>
@@ -2875,7 +2867,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C23">
         <v>90000</v>
@@ -2993,7 +2985,7 @@
     </row>
     <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11">
@@ -3182,17 +3174,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="4" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3229,7 +3221,7 @@
       </c>
       <c r="B5" s="8">
         <f>COUNTIF(Sales_Stage_Details!A:A,"Lead")</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" s="8">
         <f>SUMIF(Sales_Stage_Details!A:A,"Lead",Sales_Stage_Details!E:E)</f>
@@ -3237,18 +3229,18 @@
       </c>
       <c r="D5" s="8">
         <f>B5</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="8">
         <f>C5</f>
         <v>450000</v>
       </c>
       <c r="F5" s="8">
-        <f>COUNTIFS(Sales_Stage_Details!A5:A198,"Lead",Sales_Stage_Details!B5:B198,"This Week")</f>
-        <v>10</v>
+        <f>COUNTIFS(Sales_Stage_Details!A5:A193,"Lead",Sales_Stage_Details!B5:B193,"This Week")</f>
+        <v>8</v>
       </c>
       <c r="G5" s="8">
-        <f>SUMIFS(Sales_Stage_Details!E5:E198,Sales_Stage_Details!A5:A198,"Lead",Sales_Stage_Details!B5:B198,"This Week")</f>
+        <f>SUMIFS(Sales_Stage_Details!E5:E193,Sales_Stage_Details!A5:A193,"Lead",Sales_Stage_Details!B5:B193,"This Week")</f>
         <v>450000</v>
       </c>
       <c r="H5" s="22"/>
@@ -3259,24 +3251,24 @@
         <v>96</v>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIF(Sales_Raw_Opportunities!I4:I1000,"Active Proposal")</f>
+        <f>COUNTIF(Sales_Raw_Opportunities!I4:I999,"Active Proposal")</f>
         <v>0</v>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Sales_Raw_Opportunities!F4:F1000,Sales_Raw_Opportunities!I4:I1000,"Active Proposal")</f>
+        <f>SUMIFS(Sales_Raw_Opportunities!F4:F999,Sales_Raw_Opportunities!I4:I999,"Active Proposal")</f>
         <v>0</v>
       </c>
       <c r="D6" s="8">
-        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I1000="Active Proposal")*(Sales_Raw_Opportunities!D4:D1000=TEXT(TODAY(),"mmm yyyy")))</f>
+        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I999="Active Proposal")*(Sales_Raw_Opportunities!D4:D999=TEXT(TODAY(),"mmm yyyy")))</f>
         <v>0</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8">
-        <f>COUNTIFS(Sales_Stage_Details!A5:A198,"Active Proposal",Sales_Stage_Details!B5:B198,"This Week")</f>
+        <f>COUNTIFS(Sales_Stage_Details!A5:A193,"Active Proposal",Sales_Stage_Details!B5:B193,"This Week")</f>
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <f>SUMIFS(Sales_Stage_Details!E5:E198,Sales_Stage_Details!A5:A198,"Active Proposal",Sales_Stage_Details!B5:B198,"This Week")</f>
+        <f>SUMIFS(Sales_Stage_Details!E5:E193,Sales_Stage_Details!A5:A193,"Active Proposal",Sales_Stage_Details!B5:B193,"This Week")</f>
         <v>0</v>
       </c>
       <c r="H6" s="22"/>
@@ -3287,15 +3279,15 @@
         <v>139</v>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIF(Sales_Raw_Opportunities!I4:I1000,"Submitted")</f>
-        <v>8</v>
+        <f>COUNTIF(Sales_Raw_Opportunities!I4:I999,"Submitted")</f>
+        <v>5</v>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Sales_Raw_Opportunities!F4:F1000,Sales_Raw_Opportunities!I4:I1000,"Submitted")</f>
-        <v>2016000</v>
+        <f>SUMIFS(Sales_Raw_Opportunities!F4:F999,Sales_Raw_Opportunities!I4:I999,"Submitted")</f>
+        <v>1365000</v>
       </c>
       <c r="D7" s="8">
-        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I1000="Submitted")*(Sales_Raw_Opportunities!D4:D1000=TEXT(TODAY(),"mmm yyyy")))</f>
+        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I999="Submitted")*(Sales_Raw_Opportunities!D4:D999=TEXT(TODAY(),"mmm yyyy")))</f>
         <v>0</v>
       </c>
       <c r="E7" s="8">
@@ -3304,15 +3296,15 @@
     Sales_Raw_Opportunities!I:I,"Submitted",
     Sales_Raw_Opportunities!D:D,"&gt;"&amp;Sales_Performance!I1
 )</f>
-        <v>316000</v>
+        <v>85000</v>
       </c>
       <c r="F7" s="8">
-        <f>COUNTIFS(Sales_Stage_Details!A5:A198,"Submitted",Sales_Stage_Details!B5:B198,"This Week")</f>
-        <v>2</v>
+        <f>COUNTIFS(Sales_Stage_Details!A5:A193,"Submitted",Sales_Stage_Details!B5:B193,"This Week")</f>
+        <v>0</v>
       </c>
       <c r="G7" s="8">
-        <f>SUMIFS(Sales_Stage_Details!E5:E198,Sales_Stage_Details!A5:A198,"Submitted",Sales_Stage_Details!B5:B198,"This Week")</f>
-        <v>316000</v>
+        <f>SUMIFS(Sales_Stage_Details!E5:E193,Sales_Stage_Details!A5:A193,"Submitted",Sales_Stage_Details!B5:B193,"This Week")</f>
+        <v>0</v>
       </c>
       <c r="H7" s="22"/>
       <c r="I7" s="22"/>
@@ -3322,26 +3314,26 @@
         <v>140</v>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF(Sales_Raw_Opportunities!I4:I1000,"Won")</f>
-        <v>2</v>
+        <f>COUNTIF(Sales_Raw_Opportunities!I4:I999,"Won")</f>
+        <v>4</v>
       </c>
       <c r="C8" s="8">
-        <f>SUMIFS(Sales_Raw_Opportunities!F4:F1000,Sales_Raw_Opportunities!I4:I1000,"Won")</f>
-        <v>30000</v>
+        <f>SUMIFS(Sales_Raw_Opportunities!F4:F999,Sales_Raw_Opportunities!I4:I999,"Won")</f>
+        <v>165000</v>
       </c>
       <c r="D8" s="8">
-        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I1000="Won")*(Sales_Raw_Opportunities!D4:D1000=TEXT(TODAY(),"mmm yyyy")))</f>
+        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I999="Won")*(Sales_Raw_Opportunities!D4:D999=TEXT(TODAY(),"mmm yyyy")))</f>
         <v>0</v>
       </c>
       <c r="E8" s="8">
         <v>0</v>
       </c>
       <c r="F8" s="8">
-        <f>COUNTIFS(Sales_Stage_Details!A5:A198,"Won",Sales_Stage_Details!B5:B198,"This Week")</f>
+        <f>COUNTIFS(Sales_Stage_Details!A5:A193,"Won",Sales_Stage_Details!B5:B193,"This Week")</f>
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <f>SUMIFS(Sales_Stage_Details!E5:E198,Sales_Stage_Details!A5:A198,"Won",Sales_Stage_Details!B5:B198,"This Week")</f>
+        <f>SUMIFS(Sales_Stage_Details!E5:E193,Sales_Stage_Details!A5:A193,"Won",Sales_Stage_Details!B5:B193,"This Week")</f>
         <v>0</v>
       </c>
       <c r="H8" s="22"/>
@@ -3352,46 +3344,46 @@
         <v>141</v>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF(Sales_Raw_Opportunities!I4:I1000,"Lost")</f>
-        <v>5</v>
+        <f>COUNTIF(Sales_Raw_Opportunities!I4:I999,"Lost")</f>
+        <v>4</v>
       </c>
       <c r="C9" s="8">
-        <f>SUMIFS(Sales_Raw_Opportunities!F4:F1000,Sales_Raw_Opportunities!I4:I1000,"Lost")</f>
-        <v>430000</v>
+        <f>SUMIFS(Sales_Raw_Opportunities!F4:F999,Sales_Raw_Opportunities!I4:I999,"Lost")</f>
+        <v>355000</v>
       </c>
       <c r="D9" s="8">
-        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I1000="Lost")*(Sales_Raw_Opportunities!D4:D1000=TEXT(TODAY(),"mmm yyyy")))</f>
+        <f ca="1">SUMPRODUCT((Sales_Raw_Opportunities!I4:I999="Lost")*(Sales_Raw_Opportunities!D4:D999=TEXT(TODAY(),"mmm yyyy")))</f>
         <v>0</v>
       </c>
       <c r="E9" s="8">
         <f>SUMIFS(
     Sales_Raw_Opportunities!F:F,
     Sales_Raw_Opportunities!I:I,"Lost")</f>
-        <v>430000</v>
+        <v>355000</v>
       </c>
       <c r="F9" s="8">
-        <f>COUNTIFS(Sales_Stage_Details!A5:A198,"Lost",Sales_Stage_Details!B5:B198,"This Week")</f>
+        <f>COUNTIFS(Sales_Stage_Details!A5:A193,"Lost",Sales_Stage_Details!B5:B193,"This Week")</f>
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <f>SUMIFS(Sales_Stage_Details!E5:E198,Sales_Stage_Details!A5:A198,"Lost",Sales_Stage_Details!B5:B198,"This Week")</f>
+        <f>SUMIFS(Sales_Stage_Details!E5:E193,Sales_Stage_Details!A5:A193,"Lost",Sales_Stage_Details!B5:B193,"This Week")</f>
         <v>0</v>
       </c>
       <c r="H9" s="22"/>
       <c r="I9" s="22"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3406,7 +3398,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="36" customWidth="1"/>
@@ -3462,7 +3454,7 @@
         <v>147</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>131</v>
@@ -3480,133 +3472,133 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D4" s="30">
-        <v>46138</v>
+        <v>45894</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="11">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="G4" s="23">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H4" s="12">
         <f>IF(AND(ISNUMBER(F4),ISNUMBER(G4)),F4*G4,"")</f>
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D5" s="30">
-        <v>46131</v>
+        <v>45988</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="11">
-        <v>256000</v>
+        <v>140000</v>
       </c>
       <c r="G5" s="23">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H5" s="12">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5)),F5*G5,"")</f>
-        <v>204800</v>
+        <v>0</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J5" s="18"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D6" s="30">
-        <v>46120</v>
+        <v>45935</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="11">
-        <v>20000</v>
+        <v>400000</v>
       </c>
       <c r="G6" s="23">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="12">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6)),F6*G6,"")</f>
-        <v>16000</v>
+        <v>120000</v>
       </c>
       <c r="I6" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="D7" s="30">
+        <v>46000</v>
+      </c>
+      <c r="E7" s="30"/>
+      <c r="F7" s="11">
+        <v>500000</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="H7" s="12">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
+        <v>425000</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D7" s="30">
-        <v>46091</v>
-      </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="G7" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="12" t="str">
-        <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>157</v>
-      </c>
       <c r="J7" s="18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D8" s="30">
         <v>46083</v>
@@ -3627,15 +3619,15 @@
       </c>
       <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>107</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D9" s="30">
         <v>46054</v>
@@ -3658,609 +3650,647 @@
     </row>
     <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D10" s="30">
-        <v>46047</v>
+        <v>45991</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="11">
-        <v>90000</v>
+        <v>70000</v>
       </c>
       <c r="G10" s="23">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H10" s="12">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10)),F10*G10,"")</f>
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
       <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>123</v>
+        <v>241</v>
       </c>
       <c r="B11" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>282</v>
-      </c>
       <c r="D11" s="30">
-        <v>46040</v>
+        <v>46015</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="11">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G11" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="12">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11)),F11*G11,"")</f>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D12" s="30">
-        <v>46015</v>
+        <v>45942</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="11">
-        <v>100000</v>
-      </c>
-      <c r="G12" s="23"/>
+        <v>68000</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.5</v>
+      </c>
       <c r="H12" s="12">
         <f>F12*G12</f>
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>109</v>
+        <v>242</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D13" s="30">
-        <v>46000</v>
+        <v>46120</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="11">
-        <v>500000</v>
+        <v>20000</v>
       </c>
       <c r="G13" s="23">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H13" s="12">
         <f>F13*G13</f>
-        <v>425000</v>
+        <v>16000</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>286</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D14" s="30">
-        <v>45991</v>
+        <v>45922</v>
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="11">
-        <v>70000</v>
-      </c>
-      <c r="G14" s="23"/>
+        <v>75000</v>
+      </c>
+      <c r="G14" s="23">
+        <v>0</v>
+      </c>
       <c r="H14" s="12">
         <f>F14*G14</f>
         <v>0</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>123</v>
+        <v>244</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>262</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D15" s="30">
-        <v>45988</v>
+        <v>45890</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="11">
-        <v>140000</v>
-      </c>
-      <c r="G15" s="23"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0.5</v>
+      </c>
       <c r="H15" s="12">
         <f>F15*G15</f>
         <v>0</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D16" s="30">
-        <v>45958</v>
+        <v>46047</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="11">
-        <v>60000</v>
+        <v>90000</v>
       </c>
       <c r="G16" s="23">
         <v>0.5</v>
       </c>
       <c r="H16" s="12">
         <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16)),F16*G16,"")</f>
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D17" s="30">
-        <v>45942</v>
+        <v>45958</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="11">
-        <v>68000</v>
+        <v>60000</v>
       </c>
       <c r="G17" s="23">
         <v>0.5</v>
       </c>
       <c r="H17" s="12">
         <f>F17*G17</f>
-        <v>34000</v>
+        <v>30000</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>245</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D18" s="30">
-        <v>45935</v>
+        <v>46091</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="11">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="G18" s="23">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H18" s="12">
         <f>F18*G18</f>
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="J18" s="18"/>
+        <v>157</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>250</v>
+        <v>123</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D19" s="30">
-        <v>45922</v>
-      </c>
-      <c r="E19" s="30"/>
+        <v>46040</v>
+      </c>
+      <c r="E19" s="30">
+        <v>46055</v>
+      </c>
       <c r="F19" s="11">
-        <v>75000</v>
-      </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="12" t="str">
+        <v>30000</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1</v>
+      </c>
+      <c r="H19" s="12">
         <f>IF(AND(ISNUMBER(F19),ISNUMBER(G19)),F19*G19,"")</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D20" s="30">
-        <v>45894</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="D20" s="30"/>
       <c r="E20" s="30"/>
       <c r="F20" s="11">
-        <v>45000</v>
-      </c>
-      <c r="G20" s="23"/>
+        <v>500000</v>
+      </c>
+      <c r="G20" s="23">
+        <v>0.4</v>
+      </c>
       <c r="H20" s="12">
         <f>F20*G20</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>158</v>
+        <v>275</v>
       </c>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D21" s="30">
-        <v>45890</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="D21" s="30"/>
       <c r="E21" s="30"/>
-      <c r="F21" s="11" t="s">
-        <v>283</v>
+      <c r="F21" s="11">
+        <v>700000</v>
       </c>
       <c r="G21" s="23">
         <v>0.5</v>
       </c>
-      <c r="H21" s="12" t="str">
-        <f t="shared" ref="H21:H50" si="0">IF(AND(ISNUMBER(F21),ISNUMBER(G21)),F21*G21,"")</f>
-        <v/>
+      <c r="H21" s="12">
+        <f t="shared" ref="H21:H49" si="0">IF(AND(ISNUMBER(F21),ISNUMBER(G21)),F21*G21,"")</f>
+        <v>350000</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D22" s="30"/>
+        <v>274</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>287</v>
+      </c>
       <c r="E22" s="30"/>
       <c r="F22" s="11">
-        <v>500000</v>
+        <v>60000</v>
       </c>
       <c r="G22" s="23">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="0"/>
-        <v>200000</v>
+        <v>36000</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
       <c r="F23" s="11">
-        <v>700000</v>
+        <v>200000</v>
       </c>
       <c r="G23" s="23">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="0"/>
-        <v>350000</v>
+        <v>60000</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D24" s="30"/>
       <c r="E24" s="30"/>
       <c r="F24" s="11">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="G24" s="23">
         <v>0.3</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="J24" s="18"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D25" s="30"/>
       <c r="E25" s="30"/>
       <c r="F25" s="11">
-        <v>100000</v>
+        <v>180000</v>
       </c>
       <c r="G25" s="23">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
-        <v>30000</v>
+        <v>108000</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>284</v>
+        <v>147</v>
       </c>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D26" s="30"/>
+        <v>274</v>
+      </c>
+      <c r="D26" s="30">
+        <v>46131</v>
+      </c>
       <c r="E26" s="30"/>
       <c r="F26" s="11">
-        <v>100000</v>
+        <v>85000</v>
       </c>
       <c r="G26" s="23">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
-        <v>40000</v>
+        <v>68000</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>285</v>
+        <v>147</v>
       </c>
       <c r="J26" s="18"/>
     </row>
     <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="11">
-        <v>180000</v>
-      </c>
-      <c r="G27" s="23">
-        <v>0.6</v>
-      </c>
-      <c r="H27" s="12">
-        <f t="shared" si="0"/>
-        <v>108000</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="J27" s="18"/>
+      <c r="A27" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="11">
+        <v>70000</v>
+      </c>
+      <c r="I27" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="J27" s="24"/>
     </row>
     <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="35"/>
-      <c r="B28" s="24"/>
+      <c r="A28" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>219</v>
+      </c>
       <c r="C28" s="24"/>
       <c r="D28" s="31"/>
       <c r="E28" s="31"/>
       <c r="F28" s="25"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I28" s="33"/>
+      <c r="H28" s="11">
+        <v>50000</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>155</v>
+      </c>
       <c r="J28" s="24"/>
     </row>
     <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="35"/>
-      <c r="B29" s="24"/>
+      <c r="A29" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>220</v>
+      </c>
       <c r="C29" s="24"/>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
       <c r="F29" s="25"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I29" s="33"/>
+      <c r="H29" s="11">
+        <v>50000</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>155</v>
+      </c>
       <c r="J29" s="24"/>
     </row>
     <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="35"/>
-      <c r="B30" s="24"/>
+      <c r="A30" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>221</v>
+      </c>
       <c r="C30" s="24"/>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
       <c r="F30" s="25"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I30" s="33"/>
+      <c r="H30" s="11">
+        <v>10000</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>155</v>
+      </c>
       <c r="J30" s="24"/>
     </row>
     <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="35"/>
+      <c r="A31" s="35" t="s">
+        <v>216</v>
+      </c>
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
       <c r="D31" s="31"/>
       <c r="E31" s="31"/>
       <c r="F31" s="25"/>
       <c r="G31" s="26"/>
-      <c r="H31" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I31" s="33"/>
+      <c r="H31" s="11">
+        <v>10000</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>155</v>
+      </c>
       <c r="J31" s="24"/>
     </row>
     <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="35"/>
-      <c r="B32" s="24"/>
+      <c r="A32" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>284</v>
+      </c>
       <c r="C32" s="24"/>
       <c r="D32" s="31"/>
       <c r="E32" s="31"/>
       <c r="F32" s="25"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I32" s="33"/>
+      <c r="H32" s="11">
+        <v>200000</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>155</v>
+      </c>
       <c r="J32" s="24"/>
     </row>
     <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="35"/>
-      <c r="B33" s="24"/>
+      <c r="A33" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>222</v>
+      </c>
       <c r="C33" s="24"/>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
       <c r="F33" s="25"/>
       <c r="G33" s="26"/>
-      <c r="H33" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I33" s="33"/>
+      <c r="H33" s="11">
+        <v>10000</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>155</v>
+      </c>
       <c r="J33" s="24"/>
     </row>
     <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="35"/>
-      <c r="B34" s="24"/>
+      <c r="A34" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>286</v>
+      </c>
       <c r="C34" s="24"/>
       <c r="D34" s="31"/>
       <c r="E34" s="31"/>
       <c r="F34" s="25"/>
       <c r="G34" s="26"/>
-      <c r="H34" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I34" s="33"/>
+      <c r="H34" s="11">
+        <v>50000</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>155</v>
+      </c>
       <c r="J34" s="24"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
@@ -4488,31 +4518,16 @@
       <c r="I49" s="33"/>
       <c r="J49" s="24"/>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="35"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I50" s="33"/>
-      <c r="J50" s="24"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:J50" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <autoFilter ref="A3:J49" xr:uid="{00000000-0001-0000-0500-000000000000}">
     <filterColumn colId="8">
       <filters>
-        <filter val="Active"/>
+        <filter val="Submitted"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid stage" error="Stage must be one of: Lead, Active Proposal, Submitted, Won, Lost" sqref="I4:I9 I11:I15 I22:I1000 I17:I20" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid stage" error="Stage must be one of: Lead, Active Proposal, Submitted, Won, Lost" sqref="I4:I9 I11:I15 I17:I20 I22:I999" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Lead,Active Proposal,Submitted,Won,Lost"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4527,7 +4542,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4540,26 +4555,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4575,7 +4590,7 @@
         <v>145</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>154</v>
@@ -4595,7 +4610,7 @@
         <v>212</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E5" s="11">
         <v>70000</v>
@@ -4614,7 +4629,7 @@
         <v>213</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E6" s="11">
         <v>50000</v>
@@ -4622,7 +4637,7 @@
       <c r="F6" s="22"/>
       <c r="G6" s="18"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>155</v>
       </c>
@@ -4633,13 +4648,15 @@
         <v>214</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" s="11"/>
+        <v>220</v>
+      </c>
+      <c r="E7" s="11">
+        <v>50000</v>
+      </c>
       <c r="F7" s="22"/>
       <c r="G7" s="18"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>155</v>
       </c>
@@ -4650,15 +4667,15 @@
         <v>215</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E8" s="11">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="F8" s="22"/>
       <c r="G8" s="18"/>
     </row>
-    <row r="9" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>155</v>
       </c>
@@ -4668,11 +4685,9 @@
       <c r="C9" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>226</v>
-      </c>
+      <c r="D9" s="18"/>
       <c r="E9" s="11">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="18"/>
@@ -4685,10 +4700,10 @@
         <v>156</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="E10" s="11">
         <v>200000</v>
@@ -4704,10 +4719,10 @@
         <v>156</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E11" s="11">
         <v>10000</v>
@@ -4723,91 +4738,16 @@
         <v>156</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D12" s="18"/>
+        <v>285</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>286</v>
+      </c>
       <c r="E12" s="11">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="E13" s="11">
-        <v>10000</v>
-      </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="E15" s="11">
-        <v>60000</v>
-      </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="E16" s="11">
-        <v>256000</v>
-      </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F17" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4815,11 +4755,11 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid stage" error="Stage must be one of: Lead, Active Proposal, Submitted, Won, Lost" sqref="A5:A198" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid stage" error="Stage must be one of: Lead, Active Proposal, Submitted, Won, Lost" sqref="A5:A193" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Lead,Active Proposal,Submitted,Won,Lost"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid period" error="Period must be 'This Week' or 'This Month'" sqref="B5:B198" xr:uid="{00000000-0002-0000-0600-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid period" error="Period must be 'This Week' or 'This Month'" sqref="B5:B193" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>"This Week,This Month"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4840,18 +4780,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -4866,7 +4806,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>164</v>
@@ -4877,7 +4817,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>164</v>
@@ -4888,10 +4828,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C6" s="23">
         <v>0.75</v>
@@ -4899,10 +4839,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C7" s="23">
         <v>0.6</v>
@@ -4910,10 +4850,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C8" s="23">
         <v>0.5</v>
@@ -4921,10 +4861,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C9" s="23">
         <v>0.5</v>
@@ -4932,10 +4872,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C10" s="23">
         <v>0.8</v>
@@ -4943,10 +4883,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C11" s="23">
         <v>0.4</v>
@@ -4954,10 +4894,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C12" s="23">
         <v>0.2</v>
@@ -4965,7 +4905,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>164</v>
@@ -4976,10 +4916,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C14" s="23">
         <v>0.7</v>
@@ -4987,10 +4927,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C15" s="23">
         <v>0.7</v>
@@ -4998,10 +4938,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C16" s="23">
         <v>0.5</v>
@@ -5009,10 +4949,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C17" s="23">
         <v>0.7</v>
@@ -5040,26 +4980,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
